--- a/docs/xlsx/jobs-2026-09-14.xlsx
+++ b/docs/xlsx/jobs-2026-09-14.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="657">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1960 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>2027 Forestry Summer Internship - Chehalis WA</t>
+  </si>
+  <si>
+    <t>American Forest Management, Inc.</t>
+  </si>
+  <si>
+    <t>Chehalis, WA</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$21 - $24 per hour</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2027-forestry-summer-internship---chehalis-wa-chehalis-washington/9602335577</t>
+  </si>
+  <si>
+    <t>2027 Forestry Summer Internship - Houghton MI</t>
+  </si>
+  <si>
+    <t>Houghton, MI</t>
+  </si>
+  <si>
+    <t>$16 - $18 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2027-forestry-summer-internship---houghton-mi-houghton-michigan/1158952261</t>
+  </si>
+  <si>
+    <t>2027 Forestry Summer Internship - Ironwood MI or Florence WI</t>
+  </si>
+  <si>
+    <t>Ironwood, MI</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2027-forestry-summer-internship---ironwood-mi-or-florence-wi-ironwood-michigan/3121533721</t>
+  </si>
+  <si>
+    <t>Advocacy and Outreach Senior Coordinator</t>
+  </si>
+  <si>
+    <t>California Native Plant Society</t>
+  </si>
+  <si>
+    <t>Hybrid: Sacramento, CA</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$31.51 - $33.96 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-advocacy-and-outreach-senior-coordinator-hybrid-sacramento-california/5449858007</t>
+  </si>
+  <si>
+    <t>Area Integrated Pest Management Advisor: Commensal Rodents and Urban Wildlife (AP# 25-27)</t>
+  </si>
+  <si>
+    <t>University of California Agriculture and Natural Resources</t>
+  </si>
+  <si>
+    <t>Davis, CA</t>
+  </si>
+  <si>
+    <t>$89,100 - $113,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-area-integrated-pest-management-advisor-commensal-rodents-and-urban-wildlife-ap-25-27-davis-california/4072005175</t>
+  </si>
+  <si>
+    <t>Campaign Associate</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this entry-level position is $40,000 (but compensation may range between $40,000 and $44,450 depending on location).</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-campaign-associate-oakland-california/8032751949</t>
+  </si>
+  <si>
+    <t>Central Coast Project Manager</t>
+  </si>
+  <si>
+    <t>California State Coastal Conservancy</t>
+  </si>
+  <si>
+    <t>Oakland or San Luis Obispo, CA</t>
+  </si>
+  <si>
+    <t>$7,831 - $9,799 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-central-coast-project-manager-oakland-or-san-luis-obispo-california/8180069473</t>
+  </si>
+  <si>
+    <t>Communications Coordinator</t>
+  </si>
+  <si>
+    <t>Northwest Youth Corps</t>
+  </si>
+  <si>
+    <t>Eugene, OR</t>
+  </si>
+  <si>
+    <t>$20 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-communications-coordinator-eugene-oregon/1834315801</t>
+  </si>
+  <si>
+    <t>Conservation Advocate</t>
+  </si>
+  <si>
+    <t>Raleigh, NC</t>
+  </si>
+  <si>
+    <t>The target annual compensation for someone with 2-5 years of relevant experience is $41,750-$46,000. C</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-advocate-raleigh-north-carolina/7881835312</t>
+  </si>
+  <si>
+    <t>Conservation Engineering Technician</t>
+  </si>
+  <si>
+    <t>Shenandoah Valley Soil &amp; Water Conservation District</t>
+  </si>
+  <si>
+    <t>Harrisonburg, VA</t>
+  </si>
+  <si>
+    <t>$40,000 - $52,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-engineering-technician-harrisonburg-virginia/6693671644</t>
+  </si>
+  <si>
+    <t>Cultural Resources Technician</t>
+  </si>
+  <si>
+    <t>SWCA Environmental Consultants</t>
+  </si>
+  <si>
+    <t>Houston, TX</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$20.28 - $26.77 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-cultural-resources-technician-houston-texas/4748556714</t>
+  </si>
+  <si>
+    <t>Data Management Specialist 2 - Natural Science - West Coast Groundfish Observer Program (WCGOP) Debriefer</t>
+  </si>
+  <si>
+    <t>Pacific States Marine Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Hammond, OR</t>
+  </si>
+  <si>
+    <t>$24.26 - $38.58 per hour</t>
+  </si>
+  <si>
+    <t>ecology-fisheries-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-data-management-specialist-2---natural-science---west-coast-groundfish-observer-program-wcgop-debriefer-hammond-oregon/2937936184</t>
+  </si>
+  <si>
+    <t>Deputy Director of Program Operations</t>
+  </si>
+  <si>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>United States, Remote</t>
+  </si>
+  <si>
+    <t>$140,000 - $145,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-deputy-director-of-program-operations-united-states-remote/1785386677</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>North Olympic Land Trust</t>
+  </si>
+  <si>
+    <t>Port Angeles, WA</t>
+  </si>
+  <si>
+    <t>$65,000 - $69,680 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-development-manager-port-angeles-washington/8710282819</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Reef Renewal USA</t>
+  </si>
+  <si>
+    <t>Tampa, FL</t>
+  </si>
+  <si>
+    <t>$85,000 - $100,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-development-tampa-florida/9501872925</t>
+  </si>
+  <si>
+    <t>District Manager</t>
+  </si>
+  <si>
+    <t>Laramie County Conservation District</t>
+  </si>
+  <si>
+    <t>Cheyenne, WY</t>
+  </si>
+  <si>
+    <t>$80,000 - $100,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-district-manager-cheyenne-wyoming/3179260204</t>
+  </si>
+  <si>
+    <t>Education Programs Coordinator</t>
+  </si>
+  <si>
+    <t>The Science Zone</t>
+  </si>
+  <si>
+    <t>Casper, WY</t>
+  </si>
+  <si>
+    <t>$15 - $25 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-education-programs-coordinator-casper-wyoming/3185843721</t>
+  </si>
+  <si>
+    <t>eeCorps Environmental Educator - Bluff Lake Nature Center</t>
+  </si>
+  <si>
+    <t>Colorado Alliance for Environmental Education</t>
+  </si>
+  <si>
+    <t>Denver, CO</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$1,913.04 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-eecorps-environmental-educator---bluff-lake-nature-center-denver-colorado/6995052392</t>
+  </si>
+  <si>
+    <t>Environment New Jersey Campaign Associate</t>
+  </si>
+  <si>
+    <t>Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>The starting annual compensation for this entry-level position is $40,000 in the first year.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environment-new-jersey-campaign-associate-philadelphia-pennsylvania/6089372075</t>
+  </si>
+  <si>
+    <t>Environmental Education Internship</t>
+  </si>
+  <si>
+    <t>Fossil Rim Wildlife Center</t>
+  </si>
+  <si>
+    <t>Glen Rose, TX</t>
+  </si>
+  <si>
+    <t>$400 per month</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-education-internship-glen-rose-texas/5366825593</t>
+  </si>
+  <si>
+    <t>Environmental Organizer</t>
+  </si>
+  <si>
+    <t>Student PIRGs</t>
+  </si>
+  <si>
+    <t>San Diego, CA</t>
+  </si>
+  <si>
+    <t>The target annual compensation range for this position is $40,000 - $44,450 and depends on location, education and experience.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-organizer-san-diego-california/9847253727</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-organizer-chicago-illinois/8634492185</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Central Oregon LandWatch</t>
+  </si>
+  <si>
+    <t>Bend, OR</t>
+  </si>
+  <si>
+    <t>$160,000 - $200,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-bend-oregon/3584413072</t>
+  </si>
+  <si>
+    <t>Executive Director, Part-Time Salaried</t>
+  </si>
+  <si>
+    <t>Friends of the Tonto National Forest</t>
+  </si>
+  <si>
+    <t>Phoenix, AZ</t>
+  </si>
+  <si>
+    <t>$45,000 - $55,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-part-time-salaried-phoenix-arizona/6450803962</t>
+  </si>
+  <si>
+    <t>Forest Technician (Macon, GA)</t>
+  </si>
+  <si>
+    <t>Forest Resource Consultants, Inc.</t>
+  </si>
+  <si>
+    <t>Macon, GA</t>
+  </si>
+  <si>
+    <t>commensurate with experience</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forest-technician-macon-georgia/1531846757</t>
+  </si>
+  <si>
+    <t>Forest Technician (Quitman, MS)</t>
+  </si>
+  <si>
+    <t>Quitman, MS</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forest-technician-quitman-ms-quitman-mississippi/1015834001</t>
+  </si>
+  <si>
+    <t>Full-Time Naturalist</t>
+  </si>
+  <si>
+    <t>Somerset County Park Commission</t>
+  </si>
+  <si>
+    <t>Basking Ridge, NJ</t>
+  </si>
+  <si>
+    <t>$51,000 - $65,977 per year</t>
+  </si>
+  <si>
+    <t>environmental-education-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-full-time-naturalist-basking-ridge-new-jersey/3487967126</t>
+  </si>
+  <si>
+    <t>Grant and Technical Assistance Consultant</t>
+  </si>
+  <si>
+    <t>Southeast Climate &amp; Energy Network</t>
+  </si>
+  <si>
+    <t>Greenville, SC</t>
+  </si>
+  <si>
+    <t>$35,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-grant-and-technical-assistance-consultant-greenville-south-carolina/8046684535</t>
+  </si>
+  <si>
+    <t>Human Resources Director</t>
+  </si>
+  <si>
+    <t>Grand Canyon Trust</t>
+  </si>
+  <si>
+    <t>Flagstaff, AZ</t>
+  </si>
+  <si>
+    <t>$105,000 - $115,000 per year</t>
+  </si>
+  <si>
+    <t>Idealist</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-human-resources-director-flagstaff-arizona/4884809844</t>
+  </si>
+  <si>
+    <t>Manager of Public Policy</t>
+  </si>
+  <si>
+    <t>Western Reserve Land Conservancy</t>
+  </si>
+  <si>
+    <t>Moreland Hills, OH</t>
+  </si>
+  <si>
+    <t>$60,000 - $72,000 per year</t>
+  </si>
+  <si>
+    <t>land-trust-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-manager-of-public-policy-moreland-hills-ohio/8172551042</t>
+  </si>
+  <si>
+    <t>Oceans Advocate</t>
+  </si>
+  <si>
+    <t>The starting annual compensation range for this position is $41,750-$46,000 for a candidate with 2-5 years of experience.</t>
+  </si>
+  <si>
+    <t>marine-biology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-oceans-advocate-oakland-california/8527383600</t>
+  </si>
+  <si>
+    <t>Officer, State Decarbonization Campaign Lead</t>
+  </si>
+  <si>
+    <t>Pew Charitable Trusts</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>$121,100 - $135,400 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-officer-state-decarbonization-campaign-lead-washington-dc/9581707037</t>
+  </si>
+  <si>
+    <t>Operations and Administration Assistant</t>
+  </si>
+  <si>
+    <t>Maine Conservation Corps</t>
+  </si>
+  <si>
+    <t>Augusta, ME</t>
+  </si>
+  <si>
+    <t>$660 - $770 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations-and-administration-assistant-augusta-maine/4373942506</t>
+  </si>
+  <si>
+    <t>OPS Fish and Wildlife Biological Scientist IV-Private Lands Biologist</t>
+  </si>
+  <si>
+    <t>Florida Fish and Wildlife Conservation Commission</t>
+  </si>
+  <si>
+    <t>Marianna, FL</t>
+  </si>
+  <si>
+    <t>$24.32 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ops-fish-and-wildlife-biological-scientist-iv-private-lands-biologist-marianna-florida/5243172571</t>
+  </si>
+  <si>
+    <t>OPS Land Management Technician</t>
+  </si>
+  <si>
+    <t>University of Florida, Ordway-Swisher Biological Station</t>
+  </si>
+  <si>
+    <t>Melrose, FL</t>
+  </si>
+  <si>
+    <t>$15 - $17 per hour</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ops-land-management-technician-melrose-florida/9105093652</t>
+  </si>
+  <si>
+    <t>Outdoor Youth Education Facilitator</t>
+  </si>
+  <si>
+    <t>Sage Mountain Botanical Sanctuary</t>
+  </si>
+  <si>
+    <t>Orange, VT</t>
+  </si>
+  <si>
+    <t>Starting rate of $24/hour, commensurate with experience</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outdoor-youth-education-facilitator-orange-vermont/3391680054</t>
+  </si>
+  <si>
+    <t>Ranger I - State House - (260005YL)</t>
+  </si>
+  <si>
+    <t>Massachusetts Department of Conservation and Recreation</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>$53,822.34 - $72,700.68 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ranger-i---state-house---260005yl-boston-massachusetts/5644183960</t>
+  </si>
+  <si>
+    <t>Research Administrator</t>
+  </si>
+  <si>
+    <t>The Public Interest Network</t>
+  </si>
+  <si>
+    <t>The starting target annual compensation for this position is $40,250-$42,750.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research-administrator-denver-colorado/5021732168</t>
+  </si>
+  <si>
+    <t>Senior Associate Consultant</t>
+  </si>
+  <si>
+    <t>Davey Resource Group</t>
+  </si>
+  <si>
+    <t>Novi, MI</t>
+  </si>
+  <si>
+    <t>Compensation based on qualifications and experience.</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-associate-consultant-novi-michigan/6267608368</t>
+  </si>
+  <si>
+    <t>Senior Data Scientist</t>
+  </si>
+  <si>
+    <t>Natural State</t>
+  </si>
+  <si>
+    <t>Nairobi, Remote</t>
+  </si>
+  <si>
+    <t>$60,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-data-scientist-nairobi-remote/5756334178</t>
+  </si>
+  <si>
+    <t>STEAM Education Member</t>
+  </si>
+  <si>
+    <t>$13.80 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-steam-education-member-casper-wyoming/1124716338</t>
+  </si>
+  <si>
+    <t>Trail Apprentice</t>
+  </si>
+  <si>
+    <t>Partnership for the National Trails System (PNTS)</t>
+  </si>
+  <si>
+    <t>Washington, D.C., Remote</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>PNTS will cover all registration, travel and lodging costs for attendance at program events.</t>
+  </si>
+  <si>
+    <t>outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-trail-apprentice-washington-dc-remote/3133248470</t>
+  </si>
+  <si>
+    <t>Waterfront Assistant</t>
+  </si>
+  <si>
+    <t>The School for Field Studies</t>
+  </si>
+  <si>
+    <t>South Caicos, Turks and Caicos, Other</t>
+  </si>
+  <si>
+    <t>Salary is dependent on experience and qualifications.</t>
+  </si>
+  <si>
+    <t>marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-waterfront-assistant-south-caicos-turks-and-caicos-other/7931603689</t>
+  </si>
+  <si>
+    <t>Watershed Manager</t>
+  </si>
+  <si>
+    <t>Greenville Water</t>
+  </si>
+  <si>
+    <t>Travelers Rest, SC</t>
+  </si>
+  <si>
+    <t>Inquire</t>
+  </si>
+  <si>
+    <t>forestry-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-watershed-manager-travelers-rest-south-carolina/8395313972</t>
+  </si>
+  <si>
+    <t>Year Round Lead Camp Cousnelor</t>
+  </si>
+  <si>
+    <t>Schoolhouse Of Wonder</t>
+  </si>
+  <si>
+    <t>Durham, NC</t>
+  </si>
+  <si>
+    <t>$17 - $19 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-year-round-lead-camp-cousnelor-durham-north-carolina/3417873263</t>
+  </si>
+  <si>
+    <t>New York Program Director</t>
+  </si>
+  <si>
+    <t>Land Trust Alliance</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/new-york-program-director/</t>
+  </si>
+  <si>
+    <t>Administrative Manager</t>
+  </si>
+  <si>
+    <t>Emmanuel Gospel Center</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac25d59453d644ad8004f0143fd89821-administrative-manager-emmanuel-gospel-center-boston</t>
+  </si>
+  <si>
+    <t>Advancement Manager</t>
+  </si>
+  <si>
+    <t>The Urban Assembly</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 85350.00 - 85350.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3653084d758543cbb24c14a5c9a2fbd8-advancement-manager-the-urban-assembly-new-york</t>
+  </si>
+  <si>
+    <t>Affective Needs Teacher</t>
+  </si>
+  <si>
+    <t>KIPP Colorado Schools</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 65990.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cfe1518dca164ee68b9ca3a0a3c7c2d3-affective-needs-teacher-kipp-colorado-schools-denver</t>
+  </si>
+  <si>
+    <t>ASAP Drama Club Site Director</t>
+  </si>
+  <si>
+    <t>ASAP/After School Activities Partnerships</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 60.00 - 60.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/28fdc2305858451ba9528ec73212c943-asap-drama-club-site-director-asapafter-school-activities-partnerships-philadelphia</t>
+  </si>
+  <si>
+    <t>Assistant Director Major Gifts</t>
+  </si>
+  <si>
+    <t>NADAP</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Job Workplace, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc3f87134ed8418bac913bfc2fe4ba98-assistant-director-major-gifts-nadap-new-york</t>
+  </si>
+  <si>
+    <t>Chef - Neighborhood Center</t>
+  </si>
+  <si>
+    <t>University Settlement Society of New York</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 31.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d28bcb321ecc4059a16dd89ecab869dc-chef-neighborhood-center-university-settlement-society-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Client Services and Data Associate</t>
+  </si>
+  <si>
+    <t>The Children's Law Center NY</t>
+  </si>
+  <si>
+    <t>USD 60180.00 - 79067.32/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae829ae0f0194ac29371d881ea22dab7-client-services-and-data-associate-the-childrens-law-center-ny-new-york</t>
+  </si>
+  <si>
+    <t>Communications Specialist</t>
+  </si>
+  <si>
+    <t>National Academy of Education</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b2115ffe87fa44559777d55e1a04bf98-communications-specialist-national-academy-of-education-washington</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>Horizon Services</t>
+  </si>
+  <si>
+    <t>Hayward, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0834c8dd76be4d799700cd1f00bb909a-controller-horizon-services-hayward</t>
+  </si>
+  <si>
+    <t>Data Strategy &amp; Analytics Lead</t>
+  </si>
+  <si>
+    <t>Homeless Services Network of Central Florida</t>
+  </si>
+  <si>
+    <t>Orlando, Florida</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/435a3670bb7a4ef48858f4e2c457526c-data-strategy-analytics-lead-homeless-services-network-of-central-florida-orlando</t>
+  </si>
+  <si>
+    <t>DEPUTY DIRECTOR OF ORGANIZING</t>
+  </si>
+  <si>
+    <t>Ohio Nurses Association</t>
+  </si>
+  <si>
+    <t>Columbus, Ohio</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/47e6b523cf9c493893810e2831ea1be4-deputy-director-of-organizing-ohio-nurses-association-columbus</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Woburn, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c12d2dae916141418c639aca458b26f1-development-manager-youth-villages-woburn</t>
+  </si>
+  <si>
+    <t>Development Operations Specialist</t>
+  </si>
+  <si>
+    <t>The Circle of Care</t>
+  </si>
+  <si>
+    <t>Wilton, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f0d864cf656d41738d3f12acf8e2fe63-development-operations-specialist-the-circle-of-care-wilton</t>
+  </si>
+  <si>
+    <t>Digital Operations Specialist</t>
+  </si>
+  <si>
+    <t>Shatterproof</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f8f8367c8fd9447986ceccb8fba2ae46-digital-operations-specialist-shatterproof-washington</t>
+  </si>
+  <si>
+    <t>Direct Services Coordinator</t>
+  </si>
+  <si>
+    <t>Respect Together</t>
+  </si>
+  <si>
+    <t>Harrisburg, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 59893.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bbd02d71afdb4444bde4744988e305b4-direct-services-coordinator-respect-together-harrisburg</t>
+  </si>
+  <si>
+    <t>Director of Annual Meeting and Events</t>
+  </si>
+  <si>
+    <t>American Association of Colleges and Universities</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/11691d3ccafc4522a2fc02719d14a993-director-of-annual-meeting-and-events-american-association-of-colleges-and-universities-washington</t>
+  </si>
+  <si>
+    <t>Gemma Services</t>
+  </si>
+  <si>
+    <t>Plymouth Meeting, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54584b32ffe34e84b7ae34c446609445-director-of-development-gemma-services-plymouth-meeting</t>
+  </si>
+  <si>
+    <t>Director of Grants Development</t>
+  </si>
+  <si>
+    <t>Boston Public Health Commission</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c4831dd155524925b870d7dd625c89a5-director-of-grants-development-boston-public-health-commission-boston</t>
+  </si>
+  <si>
+    <t>Director of Institutional Giving</t>
+  </si>
+  <si>
+    <t>NYC Outward Bound Schools</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 129000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff750f5d9ef446d0a078363166ffe0c4-director-of-institutional-giving-nyc-outward-bound-schools-queens-county</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>New Bedford Research &amp; Robotics</t>
+  </si>
+  <si>
+    <t>New Bedford, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/acbc19d0394143a6be0e4741bf5bfac1-director-of-operations-new-bedford-research-robotics-new-bedford</t>
+  </si>
+  <si>
+    <t>Director of Philanthropy</t>
+  </si>
+  <si>
+    <t>CommonLit, Inc.</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/29f2aada96874f52ad454cd727c3a3ea-director-of-philanthropy-commonlit-inc-washington</t>
+  </si>
+  <si>
+    <t>Director, Advancement</t>
+  </si>
+  <si>
+    <t>District Alliance for Safe Housing</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f915984fb85d42c1b53913de65df56f7-director-advancement-district-alliance-for-safe-housing-washington</t>
+  </si>
+  <si>
+    <t>Director, Maryland Revitalization Programs Program Manager Senior II (052913)</t>
+  </si>
+  <si>
+    <t>MD DHCD</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 113157.00 - 178453.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/20a36330ec14486da21f7c18d472dbae-director-maryland-revitalization-programs-program-manager-senior-ii-052913-md-dhcd-baltimore</t>
+  </si>
+  <si>
+    <t>Education Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>Nature Forward</t>
+  </si>
+  <si>
+    <t>Chevy Chase, Maryland</t>
+  </si>
+  <si>
+    <t>USD 53000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff165d0fc06047729fd9006caaec2b91-education-administrative-coordinator-nature-forward-chevy-chase</t>
+  </si>
+  <si>
+    <t>En Médicos Sin Fronteras buscamos captadores de socios/as en vía pública para BAHIA BLANCA – Turno Mañana</t>
+  </si>
+  <si>
+    <t>MÉDICOS SIN FRONTERAS LAT</t>
+  </si>
+  <si>
+    <t>Bahía Blanca, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a569322c46a84aee8413b58943940cc9-en-medicos-sin-fronteras-buscamos-captadores-de-sociosas-en-via-publica-para-bahia-blanca-turno-manana-medicos-sin-fronteras-lat-bahia-blanca</t>
+  </si>
+  <si>
+    <t>Encargado/a de acompañamiento - Zona: San Patricio del Chañar</t>
+  </si>
+  <si>
+    <t>Fundación Cimientos (español)</t>
+  </si>
+  <si>
+    <t>San Patricio del Chañar, Neuquén, AR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b5da625127248b3ac9b4dc9ff09c5db-encargadoa-de-acompanamiento-zona-san-patricio-del-chanar-fundacion-cimientos-espanol-san-patricio-del-chanar</t>
+  </si>
+  <si>
+    <t>Equal Justice Works Fellow - Financial Empowerment Project</t>
+  </si>
+  <si>
+    <t>Legal Aid Bureau, Inc.</t>
+  </si>
+  <si>
+    <t>USD 79166.00 - 122122.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6d9e8483a8514d729b6dc16fd34205cf-equal-justice-works-fellow-financial-empowerment-project-legal-aid-bureau-inc-baltimore</t>
+  </si>
+  <si>
+    <t>Executive Assistant to the Senior Vice President, and Senior Associate, Food, Agriculture, and Natural Resources</t>
+  </si>
+  <si>
+    <t>Association of Public and Land-grant Universities</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Agriculture, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ab2d48816bcf4fcfa364a4617d0025a2-executive-assistant-to-the-senior-vice-president-and-senior-associate-food-agriculture-and-natural-resources-association-of-public-and-land-grant-universities-washington</t>
+  </si>
+  <si>
+    <t>Austin Outside</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 85000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ccfd0a00719475d9b5e91a61e11ed3f-executive-director-austin-outside-austin</t>
+  </si>
+  <si>
+    <t>Facilities Coordinator and Receptionist</t>
+  </si>
+  <si>
+    <t>Cancer Care, Inc.</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 52500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eca94caee0ae481f8a4364b4f3cf4afd-facilities-coordinator-and-receptionist-cancer-care-inc-new-york</t>
+  </si>
+  <si>
+    <t>Finance Director</t>
+  </si>
+  <si>
+    <t>Amazon Frontlines</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a26c76de1cf94dceac40d33ae39ceaa5-finance-director-amazon-frontlines-san-francisco</t>
+  </si>
+  <si>
+    <t>Full-Time Development Associate</t>
+  </si>
+  <si>
+    <t>Riverside Immigrant Services &amp; Empowerment</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Education, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a0cab41c24224d24924d55aa50ecf101-full-time-development-associate-riverside-immigrant-services-empowerment-new-york</t>
+  </si>
+  <si>
+    <t>Gift Processor and Database Associate</t>
+  </si>
+  <si>
+    <t>Sempervirens Fund</t>
+  </si>
+  <si>
+    <t>Mountain View, California</t>
+  </si>
+  <si>
+    <t>USD 29.80 - 34.60/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/53a3c914cd6b4e888ec2aa2f88ea9de1-gift-processor-and-database-associate-sempervirens-fund-mountain-view</t>
+  </si>
+  <si>
+    <t>Global Executive Director</t>
+  </si>
+  <si>
+    <t>Asylum Access</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a633932afb664b7a8d74c0b25abe8811-global-executive-director-asylum-access-oakland</t>
+  </si>
+  <si>
+    <t>Grant Manager</t>
+  </si>
+  <si>
+    <t>Meals on Wheels People, Inc.</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 64000.00 - 86650.00/year</t>
+  </si>
+  <si>
+    <t>Poverty, Seniors Retirement, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca6582134cb44a53820aa9c030c210e9-grant-manager-meals-on-wheels-people-inc-portland</t>
+  </si>
+  <si>
+    <t>Grants Manager</t>
+  </si>
+  <si>
+    <t>Israel Policy Forum</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/359d592e938b4b69a838f1ce75a210da-grants-manager-israel-policy-forum-new-york</t>
+  </si>
+  <si>
+    <t>Graphic Design and Layout (Urban Minutes and Co-Design Production)</t>
+  </si>
+  <si>
+    <t>Syrbanism gUG</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Housing Homelessness, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e069c3644a3f49b1891059cb3aa489ab-graphic-design-and-layout-urban-minutes-and-co-design-production-syrbanism-gug-berlin</t>
+  </si>
+  <si>
+    <t>Guardianship Staff Attorney-Floater</t>
+  </si>
+  <si>
+    <t>USD 79116.00 - 122122.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8894197327cb40d7b6431d863a40aac8-guardianship-staff-attorney-floater-legal-aid-bureau-inc-baltimore</t>
+  </si>
+  <si>
+    <t>Head Start Preschool Teacher - ACELC</t>
+  </si>
+  <si>
+    <t>Champlain Valley Office of Economic Opportunity</t>
+  </si>
+  <si>
+    <t>New Haven, Vermont</t>
+  </si>
+  <si>
+    <t>USD 23.73 - 28.76/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fa0c0ba8a2a44d9d856a8ddd94c67b18-head-start-preschool-teacher-acelc-champlain-valley-office-of-economic-opportunity-new-haven</t>
+  </si>
+  <si>
+    <t>Housing Stakeholder Specialist</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/141d911aff5247b8ab027622d7b40bb3-housing-stakeholder-specialist-homeless-services-network-of-central-florida-orlando</t>
+  </si>
+  <si>
+    <t>HR &amp; Operations Manager</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/33f60f808ac24bbb95463e16fa757de4-hr-operations-manager-emmanuel-gospel-center-boston</t>
+  </si>
+  <si>
+    <t>HR Assistant/HRIS Coordinator</t>
+  </si>
+  <si>
+    <t>1199 SEIU United Healthcare Workers East</t>
+  </si>
+  <si>
+    <t>USD 74999.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Job Workplace, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a8f2bddc0c474f93ab019d10481e2e19-hr-assistanthris-coordinator-1199-seiu-united-healthcare-workers-east-new-york</t>
+  </si>
+  <si>
+    <t>Human Resources Administrator</t>
+  </si>
+  <si>
+    <t>Adirondack Mountain Club</t>
+  </si>
+  <si>
+    <t>Saratoga Springs, New York</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f2d920d3ce324d60bb79ab944fee2fd7-human-resources-administrator-adirondack-mountain-club-saratoga-springs</t>
+  </si>
+  <si>
+    <t>Human Resources Business Partner</t>
+  </si>
+  <si>
+    <t>Neighborhood Health</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e988c4e622e447386204bd469af1d58-human-resources-business-partner-neighborhood-health-alexandria</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Conservation Job Board</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f7c6bd24d8d40878465390db745a373-human-resources-director-grand-canyon-trust-flagstaff</t>
+  </si>
+  <si>
+    <t>International Director</t>
+  </si>
+  <si>
+    <t>Swift Sports Organisation</t>
+  </si>
+  <si>
+    <t>USD 100.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/892dd27729e043e59fa3218757f35268-international-director-swift-sports-organisation-kampala</t>
+  </si>
+  <si>
+    <t>IT Consultant (Urban Minutes Platform)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c16504c93d0f46e68ecb37551e80cf85-it-consultant-urban-minutes-platform-syrbanism-gug-berlin</t>
+  </si>
+  <si>
+    <t>Labor Representative</t>
+  </si>
+  <si>
+    <t>USD 78412.29/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fdd4a646ee0042b4ba7778776895f8a2-labor-representative-ohio-nurses-association-columbus</t>
+  </si>
+  <si>
+    <t>Legal Assistant, Detention Project (Two-Year Fellowship)</t>
+  </si>
+  <si>
+    <t>Immigrant Legal Advocacy Project (of Maine)</t>
+  </si>
+  <si>
+    <t>Portland, Maine</t>
+  </si>
+  <si>
+    <t>USD 53045.00 - 57289.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d919215b096c4de7ac06eb9a38e9dee8-legal-assistant-detention-project-two-year-fellowship-immigrant-legal-advocacy-project-of-maine-portland</t>
+  </si>
+  <si>
+    <t>Major Gift Officer</t>
+  </si>
+  <si>
+    <t>United Way of King County (WA State)</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 89543.00 - 94256.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e5691365d7ec4a96bc0c0ae596d9e3c3-major-gift-officer-united-way-of-king-county-wa-state-seattle</t>
+  </si>
+  <si>
+    <t>Manager Quality Assurance Safe Way Forward</t>
+  </si>
+  <si>
+    <t>Safe Horizon</t>
+  </si>
+  <si>
+    <t>Staten Island, New York</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/495e989ea012476eb0e13e4e9c4c1424-manager-quality-assurance-safe-way-forward-safe-horizon-staten-island</t>
+  </si>
+  <si>
+    <t>Manager, Constituent &amp; Data Services</t>
+  </si>
+  <si>
+    <t>National Catholic Reporter</t>
+  </si>
+  <si>
+    <t>Media, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6425689a186e46b4989315c199213a89-manager-constituent-data-services-national-catholic-reporter-kansas-city</t>
+  </si>
+  <si>
+    <t>Manager, Policy, Research and Analysis</t>
+  </si>
+  <si>
+    <t>USD 137800.00 - 154000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/ae61665f3b2e480dbecf489f1a83f301-manager-policy-research-and-analysis-pew-charitable-trusts-washington</t>
+  </si>
+  <si>
+    <t>Marketing and Communications Manager</t>
+  </si>
+  <si>
+    <t>Woodstock Farm Sanctuary</t>
+  </si>
+  <si>
+    <t>High Falls, New York</t>
+  </si>
+  <si>
+    <t>Agriculture, Animals, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/451f7b3c59e34a34a2adb5c65cd75b2a-marketing-and-communications-manager-woodstock-farm-sanctuary-high-falls</t>
+  </si>
+  <si>
+    <t>Meal Deliverer - Neighborhood Center</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6023ad6f99204acb9f57188f1f6f1d67-meal-deliverer-neighborhood-center-university-settlement-society-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Green Jobs</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8b6aeb0b76d34792898d1960b2dc2b6f-new-york-program-director-land-trust-alliance-washington</t>
+  </si>
+  <si>
+    <t>Night Program Manager</t>
+  </si>
+  <si>
+    <t>Community Day Center of Waltham, Inc.</t>
+  </si>
+  <si>
+    <t>Waltham, Massachusetts</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Economic Development, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b98a5c9161c4f50826c4644b74f3678-night-program-manager-community-day-center-of-waltham-inc-waltham</t>
+  </si>
+  <si>
+    <t>Nursery Caregiver</t>
+  </si>
+  <si>
+    <t>Saint Stephen's Church</t>
+  </si>
+  <si>
+    <t>Providence, Rhode Island</t>
+  </si>
+  <si>
+    <t>USD 20.00/hour</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e12315ff6c74483186455d4af16ee844-nursery-caregiver-saint-stephens-church-providence</t>
+  </si>
+  <si>
+    <t>OFICIAL DE APOYO SEGURIDAD Y OPERACIONES</t>
+  </si>
+  <si>
+    <t>Compañeros En Salud</t>
+  </si>
+  <si>
+    <t>Ángel Albino Corzo, Chiapas, MX</t>
+  </si>
+  <si>
+    <t>MXN 18875.00 - 18875.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/df706bc260ad46c58fd7166224bf0647-oficial-de-apoyo-seguridad-y-operaciones-companeros-en-salud-angel-albino-corzo</t>
+  </si>
+  <si>
+    <t>Operations &amp; Customer Service Coordinator (Part-Time, Remote - Massachusetts)</t>
+  </si>
+  <si>
+    <t>Full Belly Foods</t>
+  </si>
+  <si>
+    <t>Remote (Massachusetts)</t>
+  </si>
+  <si>
+    <t>USD 16.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/347cda8592bb4d839c3031ded6136d10-operations-customer-service-coordinator-part-time-remote-massachusetts-full-belly-foods-boston</t>
+  </si>
+  <si>
+    <t>Operations Director</t>
+  </si>
+  <si>
+    <t>Stop Predatory Gambling Foundation</t>
+  </si>
+  <si>
+    <t>Lawrence, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Children Youth, Consumer Protection</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/605943c16ff643c498b392856fc206c8-operations-director-stop-predatory-gambling-foundation-lawrence</t>
+  </si>
+  <si>
+    <t>Organisational Communications Toolkit (Templates and Digital Assets)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fd54bb9ff3e24e01ad7e5e1cb78e3012-organisational-communications-toolkit-templates-and-digital-assets-syrbanism-gug-berlin</t>
+  </si>
+  <si>
+    <t>Parent Leadership Training Institute (PLTI) Site Coordinator</t>
+  </si>
+  <si>
+    <t>Stamford Public Education Foundation</t>
+  </si>
+  <si>
+    <t>Stamford, Connecticut</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2da056cb6d24f0bbae06e3de751746c-parent-leadership-training-institute-plti-site-coordinator-stamford-public-education-foundation-stamford</t>
+  </si>
+  <si>
+    <t>Part Time Adult Basic Education Teacher (Evenings)</t>
+  </si>
+  <si>
+    <t>District 1199C Training &amp; Upgrading Fund</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b6a1b723a5964dd19b48cce6ecd38936-part-time-adult-basic-education-teacher-evenings-district-1199c-training-upgrading-fund-philadelphia</t>
+  </si>
+  <si>
+    <t>Platform Design and Hosting (Urban Minutes)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/10b1188b8ea94f78b04aee8c61182af7-platform-design-and-hosting-urban-minutes-syrbanism-gug-berlin</t>
+  </si>
+  <si>
+    <t>Project Manager, Clinical Education</t>
+  </si>
+  <si>
+    <t>Center to Advance Palliative Care</t>
+  </si>
+  <si>
+    <t>USD 65885.00 - 98827.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cad21281e0b14c73ae0e8cba8f10b1d9-project-manager-clinical-education-center-to-advance-palliative-care-new-york</t>
+  </si>
+  <si>
+    <t>Project Manager, Solutions Insight Lab</t>
+  </si>
+  <si>
+    <t>Solutions Journalism Network</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Communications Access, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a552636d04a4e2ebd9a37c375bfa804-project-manager-solutions-insight-lab-solutions-journalism-network-new-york</t>
+  </si>
+  <si>
+    <t>School Principal - Special Education</t>
+  </si>
+  <si>
+    <t>Villa Esperanza Services</t>
+  </si>
+  <si>
+    <t>Pasadena, California</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 118000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/569d745907d84b999d32bad8f08d90a3-school-principal-special-education-villa-esperanza-services-pasadena</t>
+  </si>
+  <si>
+    <t>Senior Accountant</t>
+  </si>
+  <si>
+    <t>Bible League International</t>
+  </si>
+  <si>
+    <t>Crete, Illinois</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b2a65995804644fcbf08961e43fa9439-senior-accountant-bible-league-international-crete</t>
+  </si>
+  <si>
+    <t>Service Enriched Housing Super Hero</t>
+  </si>
+  <si>
+    <t>Community Housing Resource Partners, Inc.</t>
+  </si>
+  <si>
+    <t>Arlington, Texas</t>
+  </si>
+  <si>
+    <t>USD 16.00 - 16.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d19aa1ab95c9476c8b4b52917eb53add-service-enriched-housing-super-hero-community-housing-resource-partners-inc-arlington</t>
+  </si>
+  <si>
+    <t>Kyle, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f682375a78a4907a65f54aaef2b0db8-service-enriched-housing-super-hero-community-housing-resource-partners-inc-kyle</t>
+  </si>
+  <si>
+    <t>Laredo, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5dcbeb0cf75d45c9affc78128eebb148-service-enriched-housing-super-hero-community-housing-resource-partners-inc-laredo</t>
+  </si>
+  <si>
+    <t>Mesquite, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1bedeb88d8624ca88c582513900d86fd-service-enriched-housing-super-hero-community-housing-resource-partners-inc-mesquite</t>
+  </si>
+  <si>
+    <t>SOLAx Director of Programs &amp; Operations</t>
+  </si>
+  <si>
+    <t>SOLA—School of Leadership, Afghanistan</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/add83baab04d4bad8ca3e477fb02259a-solax-director-of-programs-operations-solaschool-of-leadership-afghanistan-providence</t>
+  </si>
+  <si>
+    <t>Sr. Manager, Portfolio &amp; Fund</t>
+  </si>
+  <si>
+    <t>GitLab Foundation</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87dcb2c5d5034d9c91b664533e05bd94-sr-manager-portfolio-fund-gitlab-foundation-san-francisco</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Volunteer Lawyers Project of the Boston Bar Association</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b48a21bb4b71435792b2f7d93e25f996-staff-attorney-volunteer-lawyers-project-of-the-boston-bar-association-boston</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Queens</t>
+  </si>
+  <si>
+    <t>USD 86700.00 - 140472.21/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Family, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50a86a127f64408c805cb482e307e951-staff-attorney-queens-the-childrens-law-center-ny-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney/Senior Staff Attorney, Detention Project</t>
+  </si>
+  <si>
+    <t>USD 74263.00 - 89116.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9609f64f3f6647a5bf24bcecb4182aa4-staff-attorneysenior-staff-attorney-detention-project-immigrant-legal-advocacy-project-of-maine-portland</t>
+  </si>
+  <si>
+    <t>Supervising Attorney</t>
+  </si>
+  <si>
+    <t>Frederick, Maryland</t>
+  </si>
+  <si>
+    <t>USD 96000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/26314321adf547fca32e8fdb18290e8b-supervising-attorney-legal-aid-bureau-inc-frederick</t>
+  </si>
+  <si>
+    <t>Towson, Maryland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dfbb8914a8924d03ba4175790609a61d-supervising-attorney-legal-aid-bureau-inc-towson</t>
+  </si>
+  <si>
+    <t>Hughesville, Maryland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b49dbc6f30dd4c56b57b1a8664160e4c-supervising-attorney-legal-aid-bureau-inc-hughesville</t>
+  </si>
+  <si>
+    <t>Supervising Attorney – Housing and Appeals</t>
+  </si>
+  <si>
+    <t>USD 103808.00 - 103808.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/af270f0c15bc4dd79ae77e3845dadb6b-supervising-attorney-housing-and-appeals-volunteer-lawyers-project-of-the-boston-bar-association-boston</t>
+  </si>
+  <si>
+    <t>Supervising Senior Attorney, Consumer Rights</t>
+  </si>
+  <si>
+    <t>Empire Justice Center</t>
+  </si>
+  <si>
+    <t>Rochester, New York</t>
+  </si>
+  <si>
+    <t>USD 104700.00 - 111000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Consumer Protection</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b36550027a0467fa0272a2a8bc0fd58-supervising-senior-attorney-consumer-rights-empire-justice-center-rochester</t>
+  </si>
+  <si>
+    <t>Team Lead - Professional Services</t>
+  </si>
+  <si>
+    <t>AutonomyWorks</t>
+  </si>
+  <si>
+    <t>Lisle, Illinois</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/313e83103a8548868837a0f9dd547f15-team-lead-professional-services-autonomyworks-lisle</t>
+  </si>
+  <si>
+    <t>Vice President, Finance and Operations</t>
+  </si>
+  <si>
+    <t>JobsFirst</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef289fc0838d4352984b4804fd565901-vice-president-finance-and-operations-jobsfirst-new-york</t>
+  </si>
+  <si>
+    <t>Volunteer Manager</t>
+  </si>
+  <si>
+    <t>Bridges to Community</t>
+  </si>
+  <si>
+    <t>San Juan de la Maguana, San Juan Province, DO</t>
+  </si>
+  <si>
+    <t>USD 1300.00 - 1300.00/month</t>
+  </si>
+  <si>
+    <t>Community Development, Volunteering, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/df3b71b792f346459099982b8a58bb4d-volunteer-manager-bridges-to-community-san-juan-de-la-maguana</t>
+  </si>
+  <si>
+    <t>Volunteer Operations Associate</t>
+  </si>
+  <si>
+    <t>Community Help in Park Slope, Inc.</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 27.50 - 29.50/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3deae262937e4906940793e835cb159a-volunteer-operations-associate-community-help-in-park-slope-inc-kings-county</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +2001,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +2027,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2409,1093 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" t="s">
+        <v>109</v>
+      </c>
+      <c r="F20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" t="s">
+        <v>115</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" t="s">
+        <v>120</v>
+      </c>
+      <c r="F22" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F23" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B24" t="s">
+        <v>125</v>
+      </c>
+      <c r="C24" t="s">
+        <v>126</v>
+      </c>
+      <c r="D24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" t="s">
+        <v>132</v>
+      </c>
+      <c r="F25" t="s">
+        <v>50</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>137</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>137</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>142</v>
+      </c>
+      <c r="B28" t="s">
+        <v>143</v>
+      </c>
+      <c r="C28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" t="s">
+        <v>145</v>
+      </c>
+      <c r="F28" t="s">
+        <v>146</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>148</v>
+      </c>
+      <c r="B29" t="s">
+        <v>149</v>
+      </c>
+      <c r="C29" t="s">
+        <v>150</v>
+      </c>
+      <c r="D29" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" t="s">
+        <v>151</v>
+      </c>
+      <c r="F29" t="s">
+        <v>50</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>153</v>
+      </c>
+      <c r="B30" t="s">
+        <v>154</v>
+      </c>
+      <c r="C30" t="s">
+        <v>155</v>
+      </c>
+      <c r="D30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" t="s">
+        <v>156</v>
+      </c>
+      <c r="F30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" t="s">
+        <v>157</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>159</v>
+      </c>
+      <c r="B31" t="s">
+        <v>160</v>
+      </c>
+      <c r="C31" t="s">
+        <v>161</v>
+      </c>
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" t="s">
+        <v>162</v>
+      </c>
+      <c r="F31" t="s">
+        <v>163</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>165</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" t="s">
+        <v>166</v>
+      </c>
+      <c r="F32" t="s">
+        <v>167</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33" t="s">
+        <v>170</v>
+      </c>
+      <c r="C33" t="s">
+        <v>171</v>
+      </c>
+      <c r="D33" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" t="s">
+        <v>173</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>175</v>
+      </c>
+      <c r="B34" t="s">
+        <v>176</v>
+      </c>
+      <c r="C34" t="s">
+        <v>177</v>
+      </c>
+      <c r="D34" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" t="s">
+        <v>178</v>
+      </c>
+      <c r="F34" t="s">
+        <v>50</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>180</v>
+      </c>
+      <c r="B35" t="s">
+        <v>181</v>
+      </c>
+      <c r="C35" t="s">
+        <v>182</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" t="s">
+        <v>183</v>
+      </c>
+      <c r="F35" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>185</v>
+      </c>
+      <c r="B36" t="s">
+        <v>186</v>
+      </c>
+      <c r="C36" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" t="s">
+        <v>188</v>
+      </c>
+      <c r="F36" t="s">
+        <v>189</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>191</v>
+      </c>
+      <c r="B37" t="s">
+        <v>192</v>
+      </c>
+      <c r="C37" t="s">
+        <v>193</v>
+      </c>
+      <c r="D37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" t="s">
+        <v>194</v>
+      </c>
+      <c r="F37" t="s">
+        <v>99</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B38" t="s">
+        <v>197</v>
+      </c>
+      <c r="C38" t="s">
+        <v>198</v>
+      </c>
+      <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" t="s">
+        <v>199</v>
+      </c>
+      <c r="F38" t="s">
+        <v>200</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>202</v>
+      </c>
+      <c r="B39" t="s">
+        <v>203</v>
+      </c>
+      <c r="C39" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" t="s">
+        <v>204</v>
+      </c>
+      <c r="F39" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>206</v>
+      </c>
+      <c r="B40" t="s">
+        <v>207</v>
+      </c>
+      <c r="C40" t="s">
+        <v>208</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" t="s">
+        <v>209</v>
+      </c>
+      <c r="F40" t="s">
+        <v>210</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>212</v>
+      </c>
+      <c r="B41" t="s">
+        <v>213</v>
+      </c>
+      <c r="C41" t="s">
+        <v>214</v>
+      </c>
+      <c r="D41" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" t="s">
+        <v>215</v>
+      </c>
+      <c r="F41" t="s">
+        <v>216</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>218</v>
+      </c>
+      <c r="B42" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42" t="s">
+        <v>97</v>
+      </c>
+      <c r="D42" t="s">
+        <v>104</v>
+      </c>
+      <c r="E42" t="s">
+        <v>219</v>
+      </c>
+      <c r="F42" t="s">
+        <v>99</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>221</v>
+      </c>
+      <c r="B43" t="s">
+        <v>222</v>
+      </c>
+      <c r="C43" t="s">
+        <v>223</v>
+      </c>
+      <c r="D43" t="s">
+        <v>224</v>
+      </c>
+      <c r="E43" t="s">
+        <v>225</v>
+      </c>
+      <c r="F43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>228</v>
+      </c>
+      <c r="B44" t="s">
+        <v>229</v>
+      </c>
+      <c r="C44" t="s">
+        <v>230</v>
+      </c>
+      <c r="D44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" t="s">
+        <v>231</v>
+      </c>
+      <c r="F44" t="s">
+        <v>232</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>234</v>
+      </c>
+      <c r="B45" t="s">
+        <v>235</v>
+      </c>
+      <c r="C45" t="s">
+        <v>236</v>
+      </c>
+      <c r="D45" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" t="s">
+        <v>237</v>
+      </c>
+      <c r="F45" t="s">
+        <v>238</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>240</v>
+      </c>
+      <c r="B46" t="s">
+        <v>241</v>
+      </c>
+      <c r="C46" t="s">
+        <v>242</v>
+      </c>
+      <c r="D46" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" t="s">
+        <v>243</v>
+      </c>
+      <c r="F46" t="s">
+        <v>226</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -466,7 +3503,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -505,8 +3542,37 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3580,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3619,2104 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F2" t="s">
+        <v>257</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F4" t="s">
+        <v>269</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D5" t="s">
+        <v>274</v>
+      </c>
+      <c r="E5" t="s">
+        <v>275</v>
+      </c>
+      <c r="F5" t="s">
+        <v>269</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>277</v>
+      </c>
+      <c r="B6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D6" t="s">
+        <v>255</v>
+      </c>
+      <c r="E6" t="s">
+        <v>279</v>
+      </c>
+      <c r="F6" t="s">
+        <v>280</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>282</v>
+      </c>
+      <c r="B7" t="s">
+        <v>283</v>
+      </c>
+      <c r="C7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E7" t="s">
+        <v>285</v>
+      </c>
+      <c r="F7" t="s">
+        <v>249</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B8" t="s">
+        <v>288</v>
+      </c>
+      <c r="C8" t="s">
+        <v>261</v>
+      </c>
+      <c r="D8" t="s">
+        <v>255</v>
+      </c>
+      <c r="E8" t="s">
+        <v>289</v>
+      </c>
+      <c r="F8" t="s">
+        <v>290</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>292</v>
+      </c>
+      <c r="B9" t="s">
+        <v>293</v>
+      </c>
+      <c r="C9" t="s">
+        <v>247</v>
+      </c>
+      <c r="D9" t="s">
+        <v>255</v>
+      </c>
+      <c r="E9" t="s">
+        <v>294</v>
+      </c>
+      <c r="F9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>296</v>
+      </c>
+      <c r="B10" t="s">
+        <v>297</v>
+      </c>
+      <c r="C10" t="s">
+        <v>298</v>
+      </c>
+      <c r="D10" t="s">
+        <v>255</v>
+      </c>
+      <c r="E10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F10" t="s">
+        <v>249</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>300</v>
+      </c>
+      <c r="B11" t="s">
+        <v>301</v>
+      </c>
+      <c r="C11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E11" t="s">
+        <v>303</v>
+      </c>
+      <c r="F11" t="s">
+        <v>304</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>306</v>
+      </c>
+      <c r="B12" t="s">
+        <v>307</v>
+      </c>
+      <c r="C12" t="s">
+        <v>308</v>
+      </c>
+      <c r="D12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E12" t="s">
+        <v>249</v>
+      </c>
+      <c r="F12" t="s">
+        <v>309</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" t="s">
+        <v>311</v>
+      </c>
+      <c r="C13" t="s">
+        <v>312</v>
+      </c>
+      <c r="D13" t="s">
+        <v>255</v>
+      </c>
+      <c r="E13" t="s">
+        <v>313</v>
+      </c>
+      <c r="F13" t="s">
+        <v>314</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>316</v>
+      </c>
+      <c r="B14" t="s">
+        <v>317</v>
+      </c>
+      <c r="C14" t="s">
+        <v>318</v>
+      </c>
+      <c r="D14" t="s">
+        <v>255</v>
+      </c>
+      <c r="E14" t="s">
+        <v>319</v>
+      </c>
+      <c r="F14" t="s">
+        <v>320</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>322</v>
+      </c>
+      <c r="B15" t="s">
+        <v>323</v>
+      </c>
+      <c r="C15" t="s">
+        <v>324</v>
+      </c>
+      <c r="D15" t="s">
+        <v>255</v>
+      </c>
+      <c r="E15" t="s">
+        <v>325</v>
+      </c>
+      <c r="F15" t="s">
+        <v>326</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>328</v>
+      </c>
+      <c r="B16" t="s">
+        <v>329</v>
+      </c>
+      <c r="C16" t="s">
+        <v>330</v>
+      </c>
+      <c r="D16" t="s">
+        <v>255</v>
+      </c>
+      <c r="E16" t="s">
+        <v>331</v>
+      </c>
+      <c r="F16" t="s">
+        <v>332</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>334</v>
+      </c>
+      <c r="B17" t="s">
+        <v>335</v>
+      </c>
+      <c r="C17" t="s">
+        <v>324</v>
+      </c>
+      <c r="D17" t="s">
+        <v>255</v>
+      </c>
+      <c r="E17" t="s">
+        <v>249</v>
+      </c>
+      <c r="F17" t="s">
+        <v>263</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" t="s">
+        <v>337</v>
+      </c>
+      <c r="C18" t="s">
+        <v>338</v>
+      </c>
+      <c r="D18" t="s">
+        <v>255</v>
+      </c>
+      <c r="E18" t="s">
+        <v>249</v>
+      </c>
+      <c r="F18" t="s">
+        <v>339</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>341</v>
+      </c>
+      <c r="B19" t="s">
+        <v>342</v>
+      </c>
+      <c r="C19" t="s">
+        <v>254</v>
+      </c>
+      <c r="D19" t="s">
+        <v>255</v>
+      </c>
+      <c r="E19" t="s">
+        <v>343</v>
+      </c>
+      <c r="F19" t="s">
+        <v>249</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>345</v>
+      </c>
+      <c r="B20" t="s">
+        <v>346</v>
+      </c>
+      <c r="C20" t="s">
+        <v>347</v>
+      </c>
+      <c r="D20" t="s">
+        <v>255</v>
+      </c>
+      <c r="E20" t="s">
+        <v>348</v>
+      </c>
+      <c r="F20" t="s">
+        <v>349</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>351</v>
+      </c>
+      <c r="B21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C21" t="s">
+        <v>353</v>
+      </c>
+      <c r="D21" t="s">
+        <v>255</v>
+      </c>
+      <c r="E21" t="s">
+        <v>354</v>
+      </c>
+      <c r="F21" t="s">
+        <v>355</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>357</v>
+      </c>
+      <c r="B22" t="s">
+        <v>358</v>
+      </c>
+      <c r="C22" t="s">
+        <v>247</v>
+      </c>
+      <c r="D22" t="s">
+        <v>255</v>
+      </c>
+      <c r="E22" t="s">
+        <v>359</v>
+      </c>
+      <c r="F22" t="s">
+        <v>360</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>362</v>
+      </c>
+      <c r="B23" t="s">
+        <v>363</v>
+      </c>
+      <c r="C23" t="s">
+        <v>324</v>
+      </c>
+      <c r="D23" t="s">
+        <v>255</v>
+      </c>
+      <c r="E23" t="s">
+        <v>364</v>
+      </c>
+      <c r="F23" t="s">
+        <v>365</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>367</v>
+      </c>
+      <c r="B24" t="s">
+        <v>368</v>
+      </c>
+      <c r="C24" t="s">
+        <v>369</v>
+      </c>
+      <c r="D24" t="s">
+        <v>255</v>
+      </c>
+      <c r="E24" t="s">
+        <v>370</v>
+      </c>
+      <c r="F24" t="s">
+        <v>371</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>373</v>
+      </c>
+      <c r="B25" t="s">
+        <v>374</v>
+      </c>
+      <c r="C25" t="s">
+        <v>375</v>
+      </c>
+      <c r="D25" t="s">
+        <v>255</v>
+      </c>
+      <c r="E25" t="s">
+        <v>376</v>
+      </c>
+      <c r="F25" t="s">
+        <v>377</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>379</v>
+      </c>
+      <c r="B26" t="s">
+        <v>380</v>
+      </c>
+      <c r="C26" t="s">
+        <v>381</v>
+      </c>
+      <c r="D26" t="s">
+        <v>284</v>
+      </c>
+      <c r="E26" t="s">
+        <v>249</v>
+      </c>
+      <c r="F26" t="s">
+        <v>309</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>383</v>
+      </c>
+      <c r="B27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C27" t="s">
+        <v>385</v>
+      </c>
+      <c r="D27" t="s">
+        <v>284</v>
+      </c>
+      <c r="E27" t="s">
+        <v>249</v>
+      </c>
+      <c r="F27" t="s">
+        <v>249</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>387</v>
+      </c>
+      <c r="B28" t="s">
+        <v>388</v>
+      </c>
+      <c r="C28" t="s">
+        <v>369</v>
+      </c>
+      <c r="D28" t="s">
+        <v>255</v>
+      </c>
+      <c r="E28" t="s">
+        <v>389</v>
+      </c>
+      <c r="F28" t="s">
+        <v>390</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>392</v>
+      </c>
+      <c r="B29" t="s">
+        <v>393</v>
+      </c>
+      <c r="C29" t="s">
+        <v>324</v>
+      </c>
+      <c r="D29" t="s">
+        <v>255</v>
+      </c>
+      <c r="E29" t="s">
+        <v>394</v>
+      </c>
+      <c r="F29" t="s">
+        <v>395</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30" t="s">
+        <v>397</v>
+      </c>
+      <c r="C30" t="s">
+        <v>398</v>
+      </c>
+      <c r="D30" t="s">
+        <v>399</v>
+      </c>
+      <c r="E30" t="s">
+        <v>400</v>
+      </c>
+      <c r="F30" t="s">
+        <v>401</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>403</v>
+      </c>
+      <c r="B31" t="s">
+        <v>404</v>
+      </c>
+      <c r="C31" t="s">
+        <v>261</v>
+      </c>
+      <c r="D31" t="s">
+        <v>255</v>
+      </c>
+      <c r="E31" t="s">
+        <v>405</v>
+      </c>
+      <c r="F31" t="s">
+        <v>249</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>407</v>
+      </c>
+      <c r="B32" t="s">
+        <v>408</v>
+      </c>
+      <c r="C32" t="s">
+        <v>409</v>
+      </c>
+      <c r="D32" t="s">
+        <v>255</v>
+      </c>
+      <c r="E32" t="s">
+        <v>410</v>
+      </c>
+      <c r="F32" t="s">
+        <v>411</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>413</v>
+      </c>
+      <c r="B33" t="s">
+        <v>414</v>
+      </c>
+      <c r="C33" t="s">
+        <v>261</v>
+      </c>
+      <c r="D33" t="s">
+        <v>255</v>
+      </c>
+      <c r="E33" t="s">
+        <v>415</v>
+      </c>
+      <c r="F33" t="s">
+        <v>416</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>418</v>
+      </c>
+      <c r="B34" t="s">
+        <v>419</v>
+      </c>
+      <c r="C34" t="s">
+        <v>420</v>
+      </c>
+      <c r="D34" t="s">
+        <v>255</v>
+      </c>
+      <c r="E34" t="s">
+        <v>421</v>
+      </c>
+      <c r="F34" t="s">
+        <v>422</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>424</v>
+      </c>
+      <c r="B35" t="s">
+        <v>425</v>
+      </c>
+      <c r="C35" t="s">
+        <v>247</v>
+      </c>
+      <c r="D35" t="s">
+        <v>255</v>
+      </c>
+      <c r="E35" t="s">
+        <v>249</v>
+      </c>
+      <c r="F35" t="s">
+        <v>426</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>428</v>
+      </c>
+      <c r="B36" t="s">
+        <v>429</v>
+      </c>
+      <c r="C36" t="s">
+        <v>430</v>
+      </c>
+      <c r="D36" t="s">
+        <v>255</v>
+      </c>
+      <c r="E36" t="s">
+        <v>431</v>
+      </c>
+      <c r="F36" t="s">
+        <v>432</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>434</v>
+      </c>
+      <c r="B37" t="s">
+        <v>435</v>
+      </c>
+      <c r="C37" t="s">
+        <v>261</v>
+      </c>
+      <c r="D37" t="s">
+        <v>255</v>
+      </c>
+      <c r="E37" t="s">
+        <v>436</v>
+      </c>
+      <c r="F37" t="s">
+        <v>437</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>439</v>
+      </c>
+      <c r="B38" t="s">
+        <v>440</v>
+      </c>
+      <c r="C38" t="s">
+        <v>247</v>
+      </c>
+      <c r="D38" t="s">
+        <v>399</v>
+      </c>
+      <c r="E38" t="s">
+        <v>249</v>
+      </c>
+      <c r="F38" t="s">
+        <v>441</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>443</v>
+      </c>
+      <c r="B39" t="s">
+        <v>388</v>
+      </c>
+      <c r="C39" t="s">
+        <v>369</v>
+      </c>
+      <c r="D39" t="s">
+        <v>255</v>
+      </c>
+      <c r="E39" t="s">
+        <v>444</v>
+      </c>
+      <c r="F39" t="s">
+        <v>390</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>446</v>
+      </c>
+      <c r="B40" t="s">
+        <v>447</v>
+      </c>
+      <c r="C40" t="s">
+        <v>448</v>
+      </c>
+      <c r="D40" t="s">
+        <v>255</v>
+      </c>
+      <c r="E40" t="s">
+        <v>449</v>
+      </c>
+      <c r="F40" t="s">
+        <v>450</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>452</v>
+      </c>
+      <c r="B41" t="s">
+        <v>301</v>
+      </c>
+      <c r="C41" t="s">
+        <v>302</v>
+      </c>
+      <c r="D41" t="s">
+        <v>255</v>
+      </c>
+      <c r="E41" t="s">
+        <v>453</v>
+      </c>
+      <c r="F41" t="s">
+        <v>304</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>455</v>
+      </c>
+      <c r="B42" t="s">
+        <v>253</v>
+      </c>
+      <c r="C42" t="s">
+        <v>254</v>
+      </c>
+      <c r="D42" t="s">
+        <v>255</v>
+      </c>
+      <c r="E42" t="s">
+        <v>456</v>
+      </c>
+      <c r="F42" t="s">
+        <v>257</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>458</v>
+      </c>
+      <c r="B43" t="s">
+        <v>459</v>
+      </c>
+      <c r="C43" t="s">
+        <v>261</v>
+      </c>
+      <c r="D43" t="s">
+        <v>255</v>
+      </c>
+      <c r="E43" t="s">
+        <v>460</v>
+      </c>
+      <c r="F43" t="s">
+        <v>461</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>463</v>
+      </c>
+      <c r="B44" t="s">
+        <v>464</v>
+      </c>
+      <c r="C44" t="s">
+        <v>465</v>
+      </c>
+      <c r="D44" t="s">
+        <v>284</v>
+      </c>
+      <c r="E44" t="s">
+        <v>466</v>
+      </c>
+      <c r="F44" t="s">
+        <v>467</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>469</v>
+      </c>
+      <c r="B45" t="s">
+        <v>470</v>
+      </c>
+      <c r="C45" t="s">
+        <v>471</v>
+      </c>
+      <c r="D45" t="s">
+        <v>255</v>
+      </c>
+      <c r="E45" t="s">
+        <v>472</v>
+      </c>
+      <c r="F45" t="s">
+        <v>249</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>153</v>
+      </c>
+      <c r="B46" t="s">
+        <v>154</v>
+      </c>
+      <c r="C46" t="s">
+        <v>155</v>
+      </c>
+      <c r="D46" t="s">
+        <v>255</v>
+      </c>
+      <c r="E46" t="s">
+        <v>474</v>
+      </c>
+      <c r="F46" t="s">
+        <v>475</v>
+      </c>
+      <c r="G46" t="s">
+        <v>476</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>478</v>
+      </c>
+      <c r="B47" t="s">
+        <v>479</v>
+      </c>
+      <c r="C47" t="s">
+        <v>247</v>
+      </c>
+      <c r="D47" t="s">
+        <v>399</v>
+      </c>
+      <c r="E47" t="s">
+        <v>480</v>
+      </c>
+      <c r="F47" t="s">
+        <v>481</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>483</v>
+      </c>
+      <c r="B48" t="s">
+        <v>440</v>
+      </c>
+      <c r="C48" t="s">
+        <v>247</v>
+      </c>
+      <c r="D48" t="s">
+        <v>399</v>
+      </c>
+      <c r="E48" t="s">
+        <v>249</v>
+      </c>
+      <c r="F48" t="s">
+        <v>441</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>485</v>
+      </c>
+      <c r="B49" t="s">
+        <v>307</v>
+      </c>
+      <c r="C49" t="s">
+        <v>308</v>
+      </c>
+      <c r="D49" t="s">
+        <v>255</v>
+      </c>
+      <c r="E49" t="s">
+        <v>486</v>
+      </c>
+      <c r="F49" t="s">
+        <v>309</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>488</v>
+      </c>
+      <c r="B50" t="s">
+        <v>489</v>
+      </c>
+      <c r="C50" t="s">
+        <v>490</v>
+      </c>
+      <c r="D50" t="s">
+        <v>255</v>
+      </c>
+      <c r="E50" t="s">
+        <v>491</v>
+      </c>
+      <c r="F50" t="s">
+        <v>492</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>494</v>
+      </c>
+      <c r="B51" t="s">
+        <v>495</v>
+      </c>
+      <c r="C51" t="s">
+        <v>496</v>
+      </c>
+      <c r="D51" t="s">
+        <v>255</v>
+      </c>
+      <c r="E51" t="s">
+        <v>497</v>
+      </c>
+      <c r="F51" t="s">
+        <v>249</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>499</v>
+      </c>
+      <c r="B52" t="s">
+        <v>500</v>
+      </c>
+      <c r="C52" t="s">
+        <v>501</v>
+      </c>
+      <c r="D52" t="s">
+        <v>255</v>
+      </c>
+      <c r="E52" t="s">
+        <v>502</v>
+      </c>
+      <c r="F52" t="s">
+        <v>249</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>504</v>
+      </c>
+      <c r="B53" t="s">
+        <v>505</v>
+      </c>
+      <c r="C53" t="s">
+        <v>247</v>
+      </c>
+      <c r="D53" t="s">
+        <v>255</v>
+      </c>
+      <c r="E53" t="s">
+        <v>394</v>
+      </c>
+      <c r="F53" t="s">
+        <v>506</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>508</v>
+      </c>
+      <c r="B54" t="s">
+        <v>170</v>
+      </c>
+      <c r="C54" t="s">
+        <v>324</v>
+      </c>
+      <c r="D54" t="s">
+        <v>255</v>
+      </c>
+      <c r="E54" t="s">
+        <v>509</v>
+      </c>
+      <c r="F54" t="s">
+        <v>249</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>511</v>
+      </c>
+      <c r="B55" t="s">
+        <v>512</v>
+      </c>
+      <c r="C55" t="s">
+        <v>513</v>
+      </c>
+      <c r="D55" t="s">
+        <v>255</v>
+      </c>
+      <c r="E55" t="s">
+        <v>415</v>
+      </c>
+      <c r="F55" t="s">
+        <v>514</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>516</v>
+      </c>
+      <c r="B56" t="s">
+        <v>283</v>
+      </c>
+      <c r="C56" t="s">
+        <v>261</v>
+      </c>
+      <c r="D56" t="s">
+        <v>284</v>
+      </c>
+      <c r="E56" t="s">
+        <v>517</v>
+      </c>
+      <c r="F56" t="s">
+        <v>249</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>245</v>
+      </c>
+      <c r="B57" t="s">
+        <v>246</v>
+      </c>
+      <c r="C57" t="s">
+        <v>519</v>
+      </c>
+      <c r="D57" t="s">
+        <v>255</v>
+      </c>
+      <c r="E57" t="s">
+        <v>520</v>
+      </c>
+      <c r="F57" t="s">
+        <v>475</v>
+      </c>
+      <c r="G57" t="s">
+        <v>521</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>523</v>
+      </c>
+      <c r="B58" t="s">
+        <v>524</v>
+      </c>
+      <c r="C58" t="s">
+        <v>525</v>
+      </c>
+      <c r="D58" t="s">
+        <v>526</v>
+      </c>
+      <c r="E58" t="s">
+        <v>527</v>
+      </c>
+      <c r="F58" t="s">
+        <v>528</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>530</v>
+      </c>
+      <c r="B59" t="s">
+        <v>531</v>
+      </c>
+      <c r="C59" t="s">
+        <v>532</v>
+      </c>
+      <c r="D59" t="s">
+        <v>284</v>
+      </c>
+      <c r="E59" t="s">
+        <v>533</v>
+      </c>
+      <c r="F59" t="s">
+        <v>534</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>536</v>
+      </c>
+      <c r="B60" t="s">
+        <v>537</v>
+      </c>
+      <c r="C60" t="s">
+        <v>538</v>
+      </c>
+      <c r="D60" t="s">
+        <v>526</v>
+      </c>
+      <c r="E60" t="s">
+        <v>539</v>
+      </c>
+      <c r="F60" t="s">
+        <v>540</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>542</v>
+      </c>
+      <c r="B61" t="s">
+        <v>543</v>
+      </c>
+      <c r="C61" t="s">
+        <v>544</v>
+      </c>
+      <c r="D61" t="s">
+        <v>284</v>
+      </c>
+      <c r="E61" t="s">
+        <v>545</v>
+      </c>
+      <c r="F61" t="s">
+        <v>546</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>548</v>
+      </c>
+      <c r="B62" t="s">
+        <v>549</v>
+      </c>
+      <c r="C62" t="s">
+        <v>550</v>
+      </c>
+      <c r="D62" t="s">
+        <v>255</v>
+      </c>
+      <c r="E62" t="s">
+        <v>551</v>
+      </c>
+      <c r="F62" t="s">
+        <v>552</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>554</v>
+      </c>
+      <c r="B63" t="s">
+        <v>440</v>
+      </c>
+      <c r="C63" t="s">
+        <v>247</v>
+      </c>
+      <c r="D63" t="s">
+        <v>399</v>
+      </c>
+      <c r="E63" t="s">
+        <v>249</v>
+      </c>
+      <c r="F63" t="s">
+        <v>441</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>556</v>
+      </c>
+      <c r="B64" t="s">
+        <v>557</v>
+      </c>
+      <c r="C64" t="s">
+        <v>558</v>
+      </c>
+      <c r="D64" t="s">
+        <v>274</v>
+      </c>
+      <c r="E64" t="s">
+        <v>527</v>
+      </c>
+      <c r="F64" t="s">
+        <v>559</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>561</v>
+      </c>
+      <c r="B65" t="s">
+        <v>562</v>
+      </c>
+      <c r="C65" t="s">
+        <v>273</v>
+      </c>
+      <c r="D65" t="s">
+        <v>284</v>
+      </c>
+      <c r="E65" t="s">
+        <v>563</v>
+      </c>
+      <c r="F65" t="s">
+        <v>263</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>565</v>
+      </c>
+      <c r="B66" t="s">
+        <v>440</v>
+      </c>
+      <c r="C66" t="s">
+        <v>247</v>
+      </c>
+      <c r="D66" t="s">
+        <v>399</v>
+      </c>
+      <c r="E66" t="s">
+        <v>249</v>
+      </c>
+      <c r="F66" t="s">
+        <v>441</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>567</v>
+      </c>
+      <c r="B67" t="s">
+        <v>568</v>
+      </c>
+      <c r="C67" t="s">
+        <v>247</v>
+      </c>
+      <c r="D67" t="s">
+        <v>255</v>
+      </c>
+      <c r="E67" t="s">
+        <v>569</v>
+      </c>
+      <c r="F67" t="s">
+        <v>309</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>571</v>
+      </c>
+      <c r="B68" t="s">
+        <v>572</v>
+      </c>
+      <c r="C68" t="s">
+        <v>247</v>
+      </c>
+      <c r="D68" t="s">
+        <v>255</v>
+      </c>
+      <c r="E68" t="s">
+        <v>325</v>
+      </c>
+      <c r="F68" t="s">
+        <v>573</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>575</v>
+      </c>
+      <c r="B69" t="s">
+        <v>576</v>
+      </c>
+      <c r="C69" t="s">
+        <v>577</v>
+      </c>
+      <c r="D69" t="s">
+        <v>255</v>
+      </c>
+      <c r="E69" t="s">
+        <v>578</v>
+      </c>
+      <c r="F69" t="s">
+        <v>579</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>581</v>
+      </c>
+      <c r="B70" t="s">
+        <v>582</v>
+      </c>
+      <c r="C70" t="s">
+        <v>583</v>
+      </c>
+      <c r="D70" t="s">
+        <v>255</v>
+      </c>
+      <c r="E70" t="s">
+        <v>394</v>
+      </c>
+      <c r="F70" t="s">
+        <v>584</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>586</v>
+      </c>
+      <c r="B71" t="s">
+        <v>587</v>
+      </c>
+      <c r="C71" t="s">
+        <v>588</v>
+      </c>
+      <c r="D71" t="s">
+        <v>284</v>
+      </c>
+      <c r="E71" t="s">
+        <v>589</v>
+      </c>
+      <c r="F71" t="s">
+        <v>249</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>586</v>
+      </c>
+      <c r="B72" t="s">
+        <v>587</v>
+      </c>
+      <c r="C72" t="s">
+        <v>591</v>
+      </c>
+      <c r="D72" t="s">
+        <v>284</v>
+      </c>
+      <c r="E72" t="s">
+        <v>589</v>
+      </c>
+      <c r="F72" t="s">
+        <v>249</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>586</v>
+      </c>
+      <c r="B73" t="s">
+        <v>587</v>
+      </c>
+      <c r="C73" t="s">
+        <v>593</v>
+      </c>
+      <c r="D73" t="s">
+        <v>284</v>
+      </c>
+      <c r="E73" t="s">
+        <v>589</v>
+      </c>
+      <c r="F73" t="s">
+        <v>249</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>586</v>
+      </c>
+      <c r="B74" t="s">
+        <v>587</v>
+      </c>
+      <c r="C74" t="s">
+        <v>595</v>
+      </c>
+      <c r="D74" t="s">
+        <v>284</v>
+      </c>
+      <c r="E74" t="s">
+        <v>589</v>
+      </c>
+      <c r="F74" t="s">
+        <v>249</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>597</v>
+      </c>
+      <c r="B75" t="s">
+        <v>598</v>
+      </c>
+      <c r="C75" t="s">
+        <v>247</v>
+      </c>
+      <c r="D75" t="s">
+        <v>255</v>
+      </c>
+      <c r="E75" t="s">
+        <v>436</v>
+      </c>
+      <c r="F75" t="s">
+        <v>599</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>601</v>
+      </c>
+      <c r="B76" t="s">
+        <v>602</v>
+      </c>
+      <c r="C76" t="s">
+        <v>247</v>
+      </c>
+      <c r="D76" t="s">
+        <v>255</v>
+      </c>
+      <c r="E76" t="s">
+        <v>474</v>
+      </c>
+      <c r="F76" t="s">
+        <v>603</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>605</v>
+      </c>
+      <c r="B77" t="s">
+        <v>606</v>
+      </c>
+      <c r="C77" t="s">
+        <v>254</v>
+      </c>
+      <c r="D77" t="s">
+        <v>255</v>
+      </c>
+      <c r="E77" t="s">
+        <v>394</v>
+      </c>
+      <c r="F77" t="s">
+        <v>607</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>609</v>
+      </c>
+      <c r="B78" t="s">
+        <v>288</v>
+      </c>
+      <c r="C78" t="s">
+        <v>261</v>
+      </c>
+      <c r="D78" t="s">
+        <v>255</v>
+      </c>
+      <c r="E78" t="s">
+        <v>610</v>
+      </c>
+      <c r="F78" t="s">
+        <v>611</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>613</v>
+      </c>
+      <c r="B79" t="s">
+        <v>489</v>
+      </c>
+      <c r="C79" t="s">
+        <v>490</v>
+      </c>
+      <c r="D79" t="s">
+        <v>255</v>
+      </c>
+      <c r="E79" t="s">
+        <v>614</v>
+      </c>
+      <c r="F79" t="s">
+        <v>492</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>616</v>
+      </c>
+      <c r="B80" t="s">
+        <v>388</v>
+      </c>
+      <c r="C80" t="s">
+        <v>617</v>
+      </c>
+      <c r="D80" t="s">
+        <v>255</v>
+      </c>
+      <c r="E80" t="s">
+        <v>618</v>
+      </c>
+      <c r="F80" t="s">
+        <v>390</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>616</v>
+      </c>
+      <c r="B81" t="s">
+        <v>388</v>
+      </c>
+      <c r="C81" t="s">
+        <v>620</v>
+      </c>
+      <c r="D81" t="s">
+        <v>255</v>
+      </c>
+      <c r="E81" t="s">
+        <v>618</v>
+      </c>
+      <c r="F81" t="s">
+        <v>390</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>616</v>
+      </c>
+      <c r="B82" t="s">
+        <v>388</v>
+      </c>
+      <c r="C82" t="s">
+        <v>622</v>
+      </c>
+      <c r="D82" t="s">
+        <v>255</v>
+      </c>
+      <c r="E82" t="s">
+        <v>618</v>
+      </c>
+      <c r="F82" t="s">
+        <v>390</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>624</v>
+      </c>
+      <c r="B83" t="s">
+        <v>606</v>
+      </c>
+      <c r="C83" t="s">
+        <v>254</v>
+      </c>
+      <c r="D83" t="s">
+        <v>255</v>
+      </c>
+      <c r="E83" t="s">
+        <v>625</v>
+      </c>
+      <c r="F83" t="s">
+        <v>626</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>628</v>
+      </c>
+      <c r="B84" t="s">
+        <v>629</v>
+      </c>
+      <c r="C84" t="s">
+        <v>630</v>
+      </c>
+      <c r="D84" t="s">
+        <v>255</v>
+      </c>
+      <c r="E84" t="s">
+        <v>631</v>
+      </c>
+      <c r="F84" t="s">
+        <v>632</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>634</v>
+      </c>
+      <c r="B85" t="s">
+        <v>635</v>
+      </c>
+      <c r="C85" t="s">
+        <v>636</v>
+      </c>
+      <c r="D85" t="s">
+        <v>255</v>
+      </c>
+      <c r="E85" t="s">
+        <v>637</v>
+      </c>
+      <c r="F85" t="s">
+        <v>638</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>640</v>
+      </c>
+      <c r="B86" t="s">
+        <v>641</v>
+      </c>
+      <c r="C86" t="s">
+        <v>261</v>
+      </c>
+      <c r="D86" t="s">
+        <v>255</v>
+      </c>
+      <c r="E86" t="s">
+        <v>642</v>
+      </c>
+      <c r="F86" t="s">
+        <v>643</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>645</v>
+      </c>
+      <c r="B87" t="s">
+        <v>646</v>
+      </c>
+      <c r="C87" t="s">
+        <v>647</v>
+      </c>
+      <c r="D87" t="s">
+        <v>255</v>
+      </c>
+      <c r="E87" t="s">
+        <v>648</v>
+      </c>
+      <c r="F87" t="s">
+        <v>649</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>651</v>
+      </c>
+      <c r="B88" t="s">
+        <v>652</v>
+      </c>
+      <c r="C88" t="s">
+        <v>653</v>
+      </c>
+      <c r="D88" t="s">
+        <v>255</v>
+      </c>
+      <c r="E88" t="s">
+        <v>654</v>
+      </c>
+      <c r="F88" t="s">
+        <v>655</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-14.xlsx
+++ b/docs/xlsx/jobs-2026-09-14.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="846">
   <si>
     <t>Title</t>
   </si>
@@ -772,6 +772,24 @@
     <t>https://greenjobs.greenjobsearch.org/jobs/new-york-program-director/</t>
   </si>
   <si>
+    <t>2027 Summer Fellow</t>
+  </si>
+  <si>
+    <t>Legal Advocates for Safe Science and Technology</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/da7039d2f88e4491b3a216b9ad72e684-2027-summer-fellow-legal-advocates-for-safe-science-and-technology-new-york</t>
+  </si>
+  <si>
     <t>Administrative Manager</t>
   </si>
   <si>
@@ -847,6 +865,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/28fdc2305858451ba9528ec73212c943-asap-drama-club-site-director-asapafter-school-activities-partnerships-philadelphia</t>
   </si>
   <si>
+    <t>Asset Manager</t>
+  </si>
+  <si>
+    <t>Mission Housing Development Corporation</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8ba4be78af2452083e180409a1476a0-asset-manager-mission-housing-development-corporation-san-francisco</t>
+  </si>
+  <si>
     <t>Assistant Director Major Gifts</t>
   </si>
   <si>
@@ -862,21 +898,117 @@
     <t>https://www.idealist.org/en/nonprofit-job/dc3f87134ed8418bac913bfc2fe4ba98-assistant-director-major-gifts-nadap-new-york</t>
   </si>
   <si>
+    <t>Associate Professor/Professor of Practice in Counseling Psychology</t>
+  </si>
+  <si>
+    <t>The American University in Cairo</t>
+  </si>
+  <si>
+    <t>New Cairo City, Cairo Governorate, EG</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c1263d2f08e542739daf55ba4c7ad77b-associate-professorprofessor-of-practice-in-counseling-psychology-the-american-university-in-cairo-new-cairo-city</t>
+  </si>
+  <si>
+    <t>Bolsista de Mobilização e Captação de Recursos Comunitários</t>
+  </si>
+  <si>
+    <t>Associação Nossa Cidade</t>
+  </si>
+  <si>
+    <t>Belo Horizonte, Minas Gerais, BR</t>
+  </si>
+  <si>
+    <t>BRL 500.00 - 500.00/month</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec405d5a79e2458d826d124e00acdbf0-bolsista-de-mobilizacao-e-captacao-de-recursos-comunitarios-associacao-nossa-cidade-belo-horizonte</t>
+  </si>
+  <si>
+    <t>Career Navigator (Part-time)</t>
+  </si>
+  <si>
+    <t>Summer Search</t>
+  </si>
+  <si>
+    <t>Bloomington, Minnesota</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/24c5259ad7b64b208153dca523132400-career-navigator-part-time-summer-search-bloomington</t>
+  </si>
+  <si>
+    <t>CCWP Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>KIWA (Koreatown Immigrant Workers Alliance)</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 70304.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bc8d2b7b023245c481b759c6f3e6af01-ccwp-administrative-coordinator-kiwa-koreatown-immigrant-workers-alliance-los-angeles</t>
+  </si>
+  <si>
+    <t>CCWP Interim Managing Director</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/68d992caf4214cd284cc473394b2b7b4-ccwp-interim-managing-director-kiwa-koreatown-immigrant-workers-alliance-los-angeles</t>
+  </si>
+  <si>
+    <t>CCWP Policy Campaign Director</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c37a44195c1e4c38809157335ebb2f1c-ccwp-policy-campaign-director-kiwa-koreatown-immigrant-workers-alliance-los-angeles</t>
+  </si>
+  <si>
     <t>Chef - Neighborhood Center</t>
   </si>
   <si>
     <t>University Settlement Society of New York</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 28.00 - 31.00/hour</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/d28bcb321ecc4059a16dd89ecab869dc-chef-neighborhood-center-university-settlement-society-of-new-york-new-york</t>
   </si>
   <si>
+    <t>Chief Program Officer</t>
+  </si>
+  <si>
+    <t>Island Conservation</t>
+  </si>
+  <si>
+    <t>Animals, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2ed588ac6d404e948d204986e7dc32a7-chief-program-officer-island-conservation-tonga</t>
+  </si>
+  <si>
     <t>Client Services and Data Associate</t>
   </si>
   <si>
@@ -892,6 +1024,57 @@
     <t>https://www.idealist.org/en/nonprofit-job/ae829ae0f0194ac29371d881ea22dab7-client-services-and-data-associate-the-childrens-law-center-ny-new-york</t>
   </si>
   <si>
+    <t>Clinical Supervisor - Safe Way Forward</t>
+  </si>
+  <si>
+    <t>Safe Horizon</t>
+  </si>
+  <si>
+    <t>Staten Island, New York</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 76000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c4ead4a9b3e541ddbe03aa1d4c352e97-clinical-supervisor-safe-way-forward-safe-horizon-staten-island</t>
+  </si>
+  <si>
+    <t>CNIB Senior Director, Donor Growth and Engagement</t>
+  </si>
+  <si>
+    <t>CNIB</t>
+  </si>
+  <si>
+    <t>Toronto, Ontario, CA</t>
+  </si>
+  <si>
+    <t>CAD 134000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Health Medicine, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/6c990b9f56684ec0ab307b1355c8b7a7-cnib-senior-director-donor-growth-and-engagement-cnib-toronto</t>
+  </si>
+  <si>
+    <t>Communications Assistant</t>
+  </si>
+  <si>
+    <t>Center for US Global Leadership</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 42500.00 - 46000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Economic Development, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/252e38b2a58342f6bb2e82773a3fb170-communications-assistant-center-for-us-global-leadership-washington</t>
+  </si>
+  <si>
     <t>Communications Specialist</t>
   </si>
   <si>
@@ -904,6 +1087,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/b2115ffe87fa44559777d55e1a04bf98-communications-specialist-national-academy-of-education-washington</t>
   </si>
   <si>
+    <t>Community Manager (Part-Time)</t>
+  </si>
+  <si>
+    <t>Editorial Freelancers Association</t>
+  </si>
+  <si>
+    <t>Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/03fed5e3fe0f495d800284c474809ed0-community-manager-part-time-editorial-freelancers-association-new-york</t>
+  </si>
+  <si>
     <t>Controller</t>
   </si>
   <si>
@@ -916,6 +1111,21 @@
     <t>https://www.idealist.org/en/job/0834c8dd76be4d799700cd1f00bb909a-controller-horizon-services-hayward</t>
   </si>
   <si>
+    <t>Counselor -Middle and High School students</t>
+  </si>
+  <si>
+    <t>Liberty LEADS in New York City</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 55.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/992788a592ca4e6594432aa38b5e5d1d-counselor-middle-and-high-school-students-liberty-leads-in-new-york-city-new-york</t>
+  </si>
+  <si>
     <t>Data Strategy &amp; Analytics Lead</t>
   </si>
   <si>
@@ -928,12 +1138,27 @@
     <t>USD 65000.00 - 75000.00/year</t>
   </si>
   <si>
-    <t>Housing Homelessness</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/435a3670bb7a4ef48858f4e2c457526c-data-strategy-analytics-lead-homeless-services-network-of-central-florida-orlando</t>
   </si>
   <si>
+    <t>Dean/Teaching Assistant</t>
+  </si>
+  <si>
+    <t>Sadie Nash Leadership Project</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6c77b968ad8140f691d53d0b46b1a46d-deanteaching-assistant-sadie-nash-leadership-project-newark</t>
+  </si>
+  <si>
     <t>DEPUTY DIRECTOR OF ORGANIZING</t>
   </si>
   <si>
@@ -988,9 +1213,6 @@
     <t>Shatterproof</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 75000.00 - 95000.00/year</t>
   </si>
   <si>
@@ -1000,6 +1222,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/f8f8367c8fd9447986ceccb8fba2ae46-digital-operations-specialist-shatterproof-washington</t>
   </si>
   <si>
+    <t>Digital Strategist</t>
+  </si>
+  <si>
+    <t>The Patients Union</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Disability, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e079688c4ac64569a5d5369b1b378373-digital-strategist-the-patients-union-new-york</t>
+  </si>
+  <si>
     <t>Direct Services Coordinator</t>
   </si>
   <si>
@@ -1087,6 +1324,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/acbc19d0394143a6be0e4741bf5bfac1-director-of-operations-new-bedford-research-robotics-new-bedford</t>
   </si>
   <si>
+    <t>Animal Welfare Institute</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Research Social Science, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a05294be044c48fcbc40ad4d735fb097-director-of-operations-animal-welfare-institute-washington</t>
+  </si>
+  <si>
     <t>Director of Philanthropy</t>
   </si>
   <si>
@@ -1102,6 +1351,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/29f2aada96874f52ad454cd727c3a3ea-director-of-philanthropy-commonlit-inc-washington</t>
   </si>
   <si>
+    <t>Director of Strategic Partnerships</t>
+  </si>
+  <si>
+    <t>The Max Foundation</t>
+  </si>
+  <si>
+    <t>USD 134475.00 - 161370.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d556f29c0444c368056ce5ba228c261-director-of-strategic-partnerships-the-max-foundation-seattle</t>
+  </si>
+  <si>
     <t>Director, Advancement</t>
   </si>
   <si>
@@ -1135,6 +1396,33 @@
     <t>https://www.idealist.org/en/government-job/20a36330ec14486da21f7c18d472dbae-director-maryland-revitalization-programs-program-manager-senior-ii-052913-md-dhcd-baltimore</t>
   </si>
   <si>
+    <t>Director, Operations, Gift Accounting, &amp; Analytics, RD</t>
+  </si>
+  <si>
+    <t>United Way of New York City</t>
+  </si>
+  <si>
+    <t>USD 80874.00 - 101971.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1606a49ca0cb434da9f37d900051b2ad-director-operations-gift-accounting-analytics-rd-united-way-of-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Director, Tax Policy</t>
+  </si>
+  <si>
+    <t>The Bipartisan Policy Center</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Housing Homelessness, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b475db87b6eb4bc6b1a658177216ccb5-director-tax-policy-the-bipartisan-policy-center-washington</t>
+  </si>
+  <si>
     <t>Education Administrative Coordinator</t>
   </si>
   <si>
@@ -1153,6 +1441,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/ff165d0fc06047729fd9006caaec2b91-education-administrative-coordinator-nature-forward-chevy-chase</t>
   </si>
   <si>
+    <t>Education Fellow / Program Coordinator</t>
+  </si>
+  <si>
+    <t>Case Method Institute for Education and Democracy</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9484c58e552f4101bfc993a87543839d-education-fellow-program-coordinator-case-method-institute-for-education-and-democracy-cambridge</t>
+  </si>
+  <si>
     <t>En Médicos Sin Fronteras buscamos captadores de socios/as en vía pública para BAHIA BLANCA – Turno Mañana</t>
   </si>
   <si>
@@ -1177,6 +1483,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/5b5da625127248b3ac9b4dc9ff09c5db-encargadoa-de-acompanamiento-zona-san-patricio-del-chanar-fundacion-cimientos-espanol-san-patricio-del-chanar</t>
   </si>
   <si>
+    <t>Environmental Science High School Teacher</t>
+  </si>
+  <si>
+    <t>USD 45.00 - 55.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4774c9b942c546bb8c028eabc9d7b428-environmental-science-high-school-teacher-liberty-leads-in-new-york-city-new-york</t>
+  </si>
+  <si>
     <t>Equal Justice Works Fellow - Financial Empowerment Project</t>
   </si>
   <si>
@@ -1192,6 +1510,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/6d9e8483a8514d729b6dc16fd34205cf-equal-justice-works-fellow-financial-empowerment-project-legal-aid-bureau-inc-baltimore</t>
   </si>
   <si>
+    <t>Executive Assistant to the President and CEO</t>
+  </si>
+  <si>
+    <t>The WNET Group</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1c39406565574231840f984b6f2e0611-executive-assistant-to-the-president-and-ceo-the-wnet-group-new-york</t>
+  </si>
+  <si>
     <t>Executive Assistant to the Senior Vice President, and Senior Associate, Food, Agriculture, and Natural Resources</t>
   </si>
   <si>
@@ -1219,12 +1552,21 @@
     <t>USD 85000.00/year</t>
   </si>
   <si>
-    <t>Civic Engagement, Community Development, Environment</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/9ccfd0a00719475d9b5e91a61e11ed3f-executive-director-austin-outside-austin</t>
   </si>
   <si>
+    <t>Progress Foundation</t>
+  </si>
+  <si>
+    <t>USD 225000.00 - 300000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/8d0add4dbe0c4a239da17fcd0dd61b78-executive-director-progress-foundation-san-francisco</t>
+  </si>
+  <si>
     <t>Facilities Coordinator and Receptionist</t>
   </si>
   <si>
@@ -1255,21 +1597,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/a26c76de1cf94dceac40d33ae39ceaa5-finance-director-amazon-frontlines-san-francisco</t>
   </si>
   <si>
+    <t>Financial Resilience Officer - Madagascar</t>
+  </si>
+  <si>
+    <t>SEED Madagascar</t>
+  </si>
+  <si>
+    <t>Taolagnaro, Anosy, MG</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/90fd7ffd0f9a47e0abc48420b3584743-financial-resilience-officer-madagascar-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
     <t>Full-Time Development Associate</t>
   </si>
   <si>
     <t>Riverside Immigrant Services &amp; Empowerment</t>
   </si>
   <si>
-    <t>USD 55000.00 - 65000.00/year</t>
-  </si>
-  <si>
     <t>Immigrants Or Refugees, Education, Civic Engagement</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/a0cab41c24224d24924d55aa50ecf101-full-time-development-associate-riverside-immigrant-services-empowerment-new-york</t>
   </si>
   <si>
+    <t>General Counsel &amp; Board Secretary</t>
+  </si>
+  <si>
+    <t>The Center for Democracy and Technology</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ad86b0177e9b4de296c84d689534c4d2-general-counsel-board-secretary-the-center-for-democracy-and-technology-washington</t>
+  </si>
+  <si>
     <t>Gift Processor and Database Associate</t>
   </si>
   <si>
@@ -1318,6 +1687,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/ca6582134cb44a53820aa9c030c210e9-grant-manager-meals-on-wheels-people-inc-portland</t>
   </si>
   <si>
+    <t>Grant Writer - Independent Contractor (5-10 hours/week)</t>
+  </si>
+  <si>
+    <t>Vivery Community</t>
+  </si>
+  <si>
+    <t>USD 55.00 - 65.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf3a0d59dc6b4a19b5747d968ff0053f-grant-writer-independent-contractor-5-10-hoursweek-vivery-community-chicago</t>
+  </si>
+  <si>
     <t>Grants Manager</t>
   </si>
   <si>
@@ -1333,6 +1717,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/359d592e938b4b69a838f1ce75a210da-grants-manager-israel-policy-forum-new-york</t>
   </si>
   <si>
+    <t>GRANTS MANAGER</t>
+  </si>
+  <si>
+    <t>Dorchester Bay Economic Development Corporation</t>
+  </si>
+  <si>
+    <t>Dorchester, MA</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/949bdf001d504139898bd5bd0af6c864-grants-manager-dorchester-bay-economic-development-corporation-dorchester</t>
+  </si>
+  <si>
     <t>Graphic Design and Layout (Urban Minutes and Co-Design Production)</t>
   </si>
   <si>
@@ -1366,9 +1768,6 @@
     <t>USD 23.73 - 28.76/hour</t>
   </si>
   <si>
-    <t>Children Youth, Education, Family</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/fa0c0ba8a2a44d9d856a8ddd94c67b18-head-start-preschool-teacher-acelc-champlain-valley-office-of-economic-opportunity-new-haven</t>
   </si>
   <si>
@@ -1438,9 +1837,6 @@
     <t>https://www.idealist.org/en/nonprofit-job/5e988c4e622e447386204bd469af1d58-human-resources-business-partner-neighborhood-health-alexandria</t>
   </si>
   <si>
-    <t>USD 105000.00 - 115000.00/year</t>
-  </si>
-  <si>
     <t>Environment</t>
   </si>
   <si>
@@ -1450,6 +1846,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/2f7c6bd24d8d40878465390db745a373-human-resources-director-grand-canyon-trust-flagstaff</t>
   </si>
   <si>
+    <t>Human Resources Manager</t>
+  </si>
+  <si>
+    <t>Capital City Public Charter School</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c2cd682e0a54e81860bf32dacd62781-human-resources-manager-capital-city-public-charter-school-washington</t>
+  </si>
+  <si>
     <t>International Director</t>
   </si>
   <si>
@@ -1465,6 +1873,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/892dd27729e043e59fa3218757f35268-international-director-swift-sports-organisation-kampala</t>
   </si>
   <si>
+    <t>IT Administrator</t>
+  </si>
+  <si>
+    <t>Open Door Legal</t>
+  </si>
+  <si>
+    <t>USD 36.78 - 44.47/hour</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a1e99b28c3834ac6b02dd9f2bba03d9b-it-administrator-open-door-legal-san-francisco</t>
+  </si>
+  <si>
     <t>IT Consultant (Urban Minutes Platform)</t>
   </si>
   <si>
@@ -1513,15 +1936,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/e5691365d7ec4a96bc0c0ae596d9e3c3-major-gift-officer-united-way-of-king-county-wa-state-seattle</t>
   </si>
   <si>
+    <t>Manager of Human Resources</t>
+  </si>
+  <si>
+    <t>Animals, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6dafca5b6f5a4c8187399ddb75f959b1-manager-of-human-resources-animal-welfare-institute-washington</t>
+  </si>
+  <si>
     <t>Manager Quality Assurance Safe Way Forward</t>
   </si>
   <si>
-    <t>Safe Horizon</t>
-  </si>
-  <si>
-    <t>Staten Island, New York</t>
-  </si>
-  <si>
     <t>USD 62000.00 - 72000.00/year</t>
   </si>
   <si>
@@ -1594,9 +2020,6 @@
     <t>Waltham, Massachusetts</t>
   </si>
   <si>
-    <t>Full Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 35.00 - 35.00/hour</t>
   </si>
   <si>
@@ -1624,6 +2047,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/e12315ff6c74483186455d4af16ee844-nursery-caregiver-saint-stephens-church-providence</t>
   </si>
   <si>
+    <t>Office Assistant (30 Hrs/Week)</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 31.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3605334b7be24954abb35b0cb816d6c8-office-assistant-30-hrsweek-editorial-freelancers-association-new-york</t>
+  </si>
+  <si>
     <t>OFICIAL DE APOYO SEGURIDAD Y OPERACIONES</t>
   </si>
   <si>
@@ -1642,6 +2074,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/df706bc260ad46c58fd7166224bf0647-oficial-de-apoyo-seguridad-y-operaciones-companeros-en-salud-angel-albino-corzo</t>
   </si>
   <si>
+    <t>Operations &amp; Communications Associate</t>
+  </si>
+  <si>
+    <t>LARC</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c46ea14574049e79e47343e98619af2-operations-communications-associate-larc-los-angeles</t>
+  </si>
+  <si>
     <t>Operations &amp; Customer Service Coordinator (Part-Time, Remote - Massachusetts)</t>
   </si>
   <si>
@@ -1678,12 +2125,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/605943c16ff643c498b392856fc206c8-operations-director-stop-predatory-gambling-foundation-lawrence</t>
   </si>
   <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Appamada</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ceb2f7f7b1d44a1ba8c17de83314071e-operations-manager-appamada-austin</t>
+  </si>
+  <si>
     <t>Organisational Communications Toolkit (Templates and Digital Assets)</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/fd54bb9ff3e24e01ad7e5e1cb78e3012-organisational-communications-toolkit-templates-and-digital-assets-syrbanism-gug-berlin</t>
   </si>
   <si>
+    <t>Outreach and Communications Coordinator</t>
+  </si>
+  <si>
+    <t>Intersectional Innovations Consulting</t>
+  </si>
+  <si>
+    <t>Community Development, Women, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/7e8d906230bb49218c3e652816113b80-outreach-and-communications-coordinator-intersectional-innovations-consulting-aurora</t>
+  </si>
+  <si>
     <t>Parent Leadership Training Institute (PLTI) Site Coordinator</t>
   </si>
   <si>
@@ -1693,9 +2164,6 @@
     <t>Stamford, Connecticut</t>
   </si>
   <si>
-    <t>Children Youth, Civic Engagement, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/c2da056cb6d24f0bbae06e3de751746c-parent-leadership-training-institute-plti-site-coordinator-stamford-public-education-foundation-stamford</t>
   </si>
   <si>
@@ -1717,6 +2185,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/10b1188b8ea94f78b04aee8c61182af7-platform-design-and-hosting-urban-minutes-syrbanism-gug-berlin</t>
   </si>
   <si>
+    <t>Program Manager, Protection Advocacy</t>
+  </si>
+  <si>
+    <t>InterAction</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Economic Development, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ea1e6b7cf9674775a69722ab6fd23a36-program-manager-protection-advocacy-interaction-washington</t>
+  </si>
+  <si>
     <t>Project Manager, Clinical Education</t>
   </si>
   <si>
@@ -1774,6 +2257,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/b2a65995804644fcbf08961e43fa9439-senior-accountant-bible-league-international-crete</t>
   </si>
   <si>
+    <t>Senior Fund Development Manager</t>
+  </si>
+  <si>
+    <t>Young Women's Freedom Center</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc5771f8c5924d23a355a8b75c83a7da-senior-fund-development-manager-young-womens-freedom-center-los-angeles</t>
+  </si>
+  <si>
+    <t>Senior Program Partner</t>
+  </si>
+  <si>
+    <t>The Christopher Family Foundation</t>
+  </si>
+  <si>
+    <t>Westmont, Illinois</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d6c77db39cb64761a6a4794fa1e628f7-senior-program-partner-the-christopher-family-foundation-westmont</t>
+  </si>
+  <si>
     <t>Service Enriched Housing Super Hero</t>
   </si>
   <si>
@@ -1807,6 +2323,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/1bedeb88d8624ca88c582513900d86fd-service-enriched-housing-super-hero-community-housing-resource-partners-inc-mesquite</t>
   </si>
   <si>
+    <t>Social Media Coordinator</t>
+  </si>
+  <si>
+    <t>Chorus LLC</t>
+  </si>
+  <si>
+    <t>Remote (Tennessee)</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/3bc035048c124916bb22eb9f55c4fdf5-social-media-coordinator-chorus-llc-nashville</t>
+  </si>
+  <si>
     <t>SOLAx Director of Programs &amp; Operations</t>
   </si>
   <si>
@@ -1843,6 +2377,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/b48a21bb4b71435792b2f7d93e25f996-staff-attorney-volunteer-lawyers-project-of-the-boston-bar-association-boston</t>
   </si>
   <si>
+    <t>Family Violence Appellate Project</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 89000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Legal Assistance, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f4e1972cdeb74f76adf99ac41cb63637-staff-attorney-family-violence-appellate-project-oakland</t>
+  </si>
+  <si>
     <t>Staff Attorney, Queens</t>
   </si>
   <si>
@@ -1949,6 +2498,24 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/ef289fc0838d4352984b4804fd565901-vice-president-finance-and-operations-jobsfirst-new-york</t>
+  </si>
+  <si>
+    <t>Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>Westchester Community College Foundation</t>
+  </si>
+  <si>
+    <t>Valhalla, New York</t>
+  </si>
+  <si>
+    <t>USD 74384.00 - 92149.00/year</t>
+  </si>
+  <si>
+    <t>Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/52cf75951fee4396ada62e057e8a6623-volunteer-coordinator-westchester-community-college-foundation-valhalla</t>
   </si>
   <si>
     <t>Volunteer Manager</t>
@@ -3580,7 +4147,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3627,33 +4194,33 @@
         <v>253</v>
       </c>
       <c r="C2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" t="s">
         <v>254</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>255</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>256</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B3" t="s">
         <v>259</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>260</v>
       </c>
-      <c r="C3" t="s">
-        <v>261</v>
-      </c>
       <c r="D3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E3" t="s">
         <v>262</v>
@@ -3676,7 +4243,7 @@
         <v>267</v>
       </c>
       <c r="D4" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E4" t="s">
         <v>268</v>
@@ -3699,13 +4266,13 @@
         <v>273</v>
       </c>
       <c r="D5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E5" t="s">
         <v>274</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>275</v>
-      </c>
-      <c r="F5" t="s">
-        <v>269</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>276</v>
@@ -3719,277 +4286,277 @@
         <v>278</v>
       </c>
       <c r="C6" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="D6" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="E6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F6" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C7" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="D7" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="E7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F7" t="s">
-        <v>249</v>
+        <v>287</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C8" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D8" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="D9" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E9" t="s">
-        <v>294</v>
+        <v>249</v>
       </c>
       <c r="F9" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B10" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C10" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D10" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="E10" t="s">
-        <v>249</v>
+        <v>302</v>
       </c>
       <c r="F10" t="s">
-        <v>249</v>
+        <v>303</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B11" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C11" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D11" t="s">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="E11" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="F11" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B12" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C12" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="D12" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E12" t="s">
-        <v>249</v>
+        <v>315</v>
       </c>
       <c r="F12" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>318</v>
       </c>
       <c r="B13" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E13" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F13" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B14" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C14" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D14" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E14" t="s">
         <v>319</v>
       </c>
       <c r="F14" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B15" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C15" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
       <c r="D15" t="s">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="E15" t="s">
         <v>325</v>
       </c>
       <c r="F15" t="s">
+        <v>249</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>327</v>
+      </c>
+      <c r="B16" t="s">
         <v>328</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>247</v>
+      </c>
+      <c r="D16" t="s">
+        <v>261</v>
+      </c>
+      <c r="E16" t="s">
+        <v>249</v>
+      </c>
+      <c r="F16" t="s">
         <v>329</v>
       </c>
-      <c r="C16" t="s">
+      <c r="H16" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="D16" t="s">
-        <v>255</v>
-      </c>
-      <c r="E16" t="s">
-        <v>331</v>
-      </c>
-      <c r="F16" t="s">
-        <v>332</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>331</v>
+      </c>
+      <c r="B17" t="s">
+        <v>332</v>
+      </c>
+      <c r="C17" t="s">
+        <v>267</v>
+      </c>
+      <c r="D17" t="s">
+        <v>261</v>
+      </c>
+      <c r="E17" t="s">
+        <v>333</v>
+      </c>
+      <c r="F17" t="s">
         <v>334</v>
       </c>
-      <c r="B17" t="s">
+      <c r="H17" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="C17" t="s">
-        <v>324</v>
-      </c>
-      <c r="D17" t="s">
-        <v>255</v>
-      </c>
-      <c r="E17" t="s">
-        <v>249</v>
-      </c>
-      <c r="F17" t="s">
-        <v>263</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="B18" t="s">
         <v>337</v>
@@ -3998,13 +4565,13 @@
         <v>338</v>
       </c>
       <c r="D18" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E18" t="s">
+        <v>339</v>
+      </c>
+      <c r="F18" t="s">
         <v>249</v>
-      </c>
-      <c r="F18" t="s">
-        <v>339</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>340</v>
@@ -4018,62 +4585,62 @@
         <v>342</v>
       </c>
       <c r="C19" t="s">
-        <v>254</v>
+        <v>343</v>
       </c>
       <c r="D19" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F19" t="s">
-        <v>249</v>
+        <v>345</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B20" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C20" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D20" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E20" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F20" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B21" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C21" t="s">
-        <v>353</v>
+        <v>247</v>
       </c>
       <c r="D21" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E21" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F21" t="s">
-        <v>355</v>
+        <v>269</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>356</v>
@@ -4090,168 +4657,168 @@
         <v>247</v>
       </c>
       <c r="D22" t="s">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="E22" t="s">
+        <v>249</v>
+      </c>
+      <c r="F22" t="s">
         <v>359</v>
       </c>
-      <c r="F22" t="s">
+      <c r="H22" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>361</v>
+      </c>
+      <c r="B23" t="s">
         <v>362</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>363</v>
       </c>
-      <c r="C23" t="s">
-        <v>324</v>
-      </c>
       <c r="D23" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E23" t="s">
+        <v>249</v>
+      </c>
+      <c r="F23" t="s">
+        <v>249</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="F23" t="s">
-        <v>365</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>365</v>
+      </c>
+      <c r="B24" t="s">
+        <v>366</v>
+      </c>
+      <c r="C24" t="s">
+        <v>267</v>
+      </c>
+      <c r="D24" t="s">
+        <v>308</v>
+      </c>
+      <c r="E24" t="s">
         <v>367</v>
       </c>
-      <c r="B24" t="s">
+      <c r="F24" t="s">
         <v>368</v>
       </c>
-      <c r="C24" t="s">
+      <c r="H24" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="D24" t="s">
-        <v>255</v>
-      </c>
-      <c r="E24" t="s">
-        <v>370</v>
-      </c>
-      <c r="F24" t="s">
-        <v>371</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>370</v>
+      </c>
+      <c r="B25" t="s">
+        <v>371</v>
+      </c>
+      <c r="C25" t="s">
+        <v>372</v>
+      </c>
+      <c r="D25" t="s">
+        <v>261</v>
+      </c>
+      <c r="E25" t="s">
         <v>373</v>
       </c>
-      <c r="B25" t="s">
+      <c r="F25" t="s">
+        <v>287</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="C25" t="s">
-        <v>375</v>
-      </c>
-      <c r="D25" t="s">
-        <v>255</v>
-      </c>
-      <c r="E25" t="s">
-        <v>376</v>
-      </c>
-      <c r="F25" t="s">
-        <v>377</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>375</v>
+      </c>
+      <c r="B26" t="s">
+        <v>376</v>
+      </c>
+      <c r="C26" t="s">
+        <v>377</v>
+      </c>
+      <c r="D26" t="s">
+        <v>280</v>
+      </c>
+      <c r="E26" t="s">
+        <v>378</v>
+      </c>
+      <c r="F26" t="s">
         <v>379</v>
       </c>
-      <c r="B26" t="s">
+      <c r="H26" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="C26" t="s">
-        <v>381</v>
-      </c>
-      <c r="D26" t="s">
-        <v>284</v>
-      </c>
-      <c r="E26" t="s">
-        <v>249</v>
-      </c>
-      <c r="F26" t="s">
-        <v>309</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>381</v>
+      </c>
+      <c r="B27" t="s">
+        <v>382</v>
+      </c>
+      <c r="C27" t="s">
         <v>383</v>
       </c>
-      <c r="B27" t="s">
-        <v>384</v>
-      </c>
-      <c r="C27" t="s">
-        <v>385</v>
-      </c>
       <c r="D27" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="E27" t="s">
         <v>249</v>
       </c>
       <c r="F27" t="s">
-        <v>249</v>
+        <v>384</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" t="s">
+        <v>386</v>
+      </c>
+      <c r="C28" t="s">
         <v>387</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28" t="s">
+        <v>261</v>
+      </c>
+      <c r="E28" t="s">
         <v>388</v>
       </c>
-      <c r="C28" t="s">
-        <v>369</v>
-      </c>
-      <c r="D28" t="s">
-        <v>255</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>389</v>
       </c>
-      <c r="F28" t="s">
+      <c r="H28" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>391</v>
+      </c>
+      <c r="B29" t="s">
         <v>392</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>393</v>
       </c>
-      <c r="C29" t="s">
-        <v>324</v>
-      </c>
       <c r="D29" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E29" t="s">
         <v>394</v>
@@ -4265,45 +4832,45 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>124</v>
+        <v>397</v>
       </c>
       <c r="B30" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C30" t="s">
-        <v>398</v>
+        <v>349</v>
       </c>
       <c r="D30" t="s">
+        <v>261</v>
+      </c>
+      <c r="E30" t="s">
         <v>399</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>400</v>
       </c>
-      <c r="F30" t="s">
+      <c r="H30" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>402</v>
+      </c>
+      <c r="B31" t="s">
         <v>403</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
+        <v>247</v>
+      </c>
+      <c r="D31" t="s">
+        <v>261</v>
+      </c>
+      <c r="E31" t="s">
         <v>404</v>
       </c>
-      <c r="C31" t="s">
-        <v>261</v>
-      </c>
-      <c r="D31" t="s">
-        <v>255</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>405</v>
-      </c>
-      <c r="F31" t="s">
-        <v>249</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>406</v>
@@ -4320,7 +4887,7 @@
         <v>409</v>
       </c>
       <c r="D32" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E32" t="s">
         <v>410</v>
@@ -4340,263 +4907,263 @@
         <v>414</v>
       </c>
       <c r="C33" t="s">
-        <v>261</v>
+        <v>349</v>
       </c>
       <c r="D33" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E33" t="s">
+        <v>249</v>
+      </c>
+      <c r="F33" t="s">
+        <v>269</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="F33" t="s">
-        <v>416</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" t="s">
+        <v>416</v>
+      </c>
+      <c r="C34" t="s">
+        <v>417</v>
+      </c>
+      <c r="D34" t="s">
+        <v>261</v>
+      </c>
+      <c r="E34" t="s">
+        <v>249</v>
+      </c>
+      <c r="F34" t="s">
         <v>418</v>
       </c>
-      <c r="B34" t="s">
+      <c r="H34" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="C34" t="s">
-        <v>420</v>
-      </c>
-      <c r="D34" t="s">
-        <v>255</v>
-      </c>
-      <c r="E34" t="s">
-        <v>421</v>
-      </c>
-      <c r="F34" t="s">
-        <v>422</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B35" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C35" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="D35" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E35" t="s">
+        <v>422</v>
+      </c>
+      <c r="F35" t="s">
         <v>249</v>
       </c>
-      <c r="F35" t="s">
-        <v>426</v>
-      </c>
       <c r="H35" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>424</v>
+      </c>
+      <c r="B36" t="s">
+        <v>425</v>
+      </c>
+      <c r="C36" t="s">
+        <v>426</v>
+      </c>
+      <c r="D36" t="s">
+        <v>261</v>
+      </c>
+      <c r="E36" t="s">
+        <v>427</v>
+      </c>
+      <c r="F36" t="s">
         <v>428</v>
       </c>
-      <c r="B36" t="s">
+      <c r="H36" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="C36" t="s">
-        <v>430</v>
-      </c>
-      <c r="D36" t="s">
-        <v>255</v>
-      </c>
-      <c r="E36" t="s">
-        <v>431</v>
-      </c>
-      <c r="F36" t="s">
-        <v>432</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>430</v>
+      </c>
+      <c r="B37" t="s">
+        <v>431</v>
+      </c>
+      <c r="C37" t="s">
+        <v>432</v>
+      </c>
+      <c r="D37" t="s">
+        <v>261</v>
+      </c>
+      <c r="E37" t="s">
+        <v>433</v>
+      </c>
+      <c r="F37" t="s">
         <v>434</v>
       </c>
-      <c r="B37" t="s">
+      <c r="H37" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="C37" t="s">
-        <v>261</v>
-      </c>
-      <c r="D37" t="s">
-        <v>255</v>
-      </c>
-      <c r="E37" t="s">
-        <v>436</v>
-      </c>
-      <c r="F37" t="s">
-        <v>437</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>430</v>
+      </c>
+      <c r="B38" t="s">
+        <v>436</v>
+      </c>
+      <c r="C38" t="s">
+        <v>349</v>
+      </c>
+      <c r="D38" t="s">
+        <v>261</v>
+      </c>
+      <c r="E38" t="s">
+        <v>437</v>
+      </c>
+      <c r="F38" t="s">
+        <v>438</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="B38" t="s">
-        <v>440</v>
-      </c>
-      <c r="C38" t="s">
-        <v>247</v>
-      </c>
-      <c r="D38" t="s">
-        <v>399</v>
-      </c>
-      <c r="E38" t="s">
-        <v>249</v>
-      </c>
-      <c r="F38" t="s">
-        <v>441</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>440</v>
+      </c>
+      <c r="B39" t="s">
+        <v>441</v>
+      </c>
+      <c r="C39" t="s">
+        <v>247</v>
+      </c>
+      <c r="D39" t="s">
+        <v>261</v>
+      </c>
+      <c r="E39" t="s">
+        <v>442</v>
+      </c>
+      <c r="F39" t="s">
         <v>443</v>
       </c>
-      <c r="B39" t="s">
-        <v>388</v>
-      </c>
-      <c r="C39" t="s">
-        <v>369</v>
-      </c>
-      <c r="D39" t="s">
-        <v>255</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="H39" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="F39" t="s">
-        <v>390</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>445</v>
+      </c>
+      <c r="B40" t="s">
         <v>446</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
+        <v>247</v>
+      </c>
+      <c r="D40" t="s">
+        <v>261</v>
+      </c>
+      <c r="E40" t="s">
         <v>447</v>
       </c>
-      <c r="C40" t="s">
+      <c r="F40" t="s">
+        <v>249</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="D40" t="s">
-        <v>255</v>
-      </c>
-      <c r="E40" t="s">
-        <v>449</v>
-      </c>
-      <c r="F40" t="s">
-        <v>450</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>449</v>
+      </c>
+      <c r="B41" t="s">
+        <v>450</v>
+      </c>
+      <c r="C41" t="s">
+        <v>349</v>
+      </c>
+      <c r="D41" t="s">
+        <v>261</v>
+      </c>
+      <c r="E41" t="s">
+        <v>451</v>
+      </c>
+      <c r="F41" t="s">
         <v>452</v>
       </c>
-      <c r="B41" t="s">
-        <v>301</v>
-      </c>
-      <c r="C41" t="s">
-        <v>302</v>
-      </c>
-      <c r="D41" t="s">
-        <v>255</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="H41" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="F41" t="s">
-        <v>304</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>454</v>
+      </c>
+      <c r="B42" t="s">
         <v>455</v>
       </c>
-      <c r="B42" t="s">
-        <v>253</v>
-      </c>
       <c r="C42" t="s">
-        <v>254</v>
+        <v>456</v>
       </c>
       <c r="D42" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E42" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F42" t="s">
-        <v>257</v>
+        <v>458</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B43" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D43" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E43" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F43" t="s">
-        <v>461</v>
+        <v>249</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B44" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C44" t="s">
-        <v>465</v>
+        <v>349</v>
       </c>
       <c r="D44" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="E44" t="s">
         <v>466</v>
@@ -4619,1011 +5186,1954 @@
         <v>471</v>
       </c>
       <c r="D45" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E45" t="s">
         <v>472</v>
       </c>
       <c r="F45" t="s">
-        <v>249</v>
+        <v>473</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>153</v>
+        <v>475</v>
       </c>
       <c r="B46" t="s">
-        <v>154</v>
+        <v>476</v>
       </c>
       <c r="C46" t="s">
-        <v>155</v>
+        <v>477</v>
       </c>
       <c r="D46" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E46" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="F46" t="s">
-        <v>475</v>
-      </c>
-      <c r="G46" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B47" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C47" t="s">
-        <v>247</v>
+        <v>483</v>
       </c>
       <c r="D47" t="s">
-        <v>399</v>
+        <v>308</v>
       </c>
       <c r="E47" t="s">
-        <v>480</v>
+        <v>249</v>
       </c>
       <c r="F47" t="s">
-        <v>481</v>
+        <v>384</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B48" t="s">
-        <v>440</v>
+        <v>486</v>
       </c>
       <c r="C48" t="s">
-        <v>247</v>
+        <v>487</v>
       </c>
       <c r="D48" t="s">
-        <v>399</v>
+        <v>308</v>
       </c>
       <c r="E48" t="s">
         <v>249</v>
       </c>
       <c r="F48" t="s">
-        <v>441</v>
+        <v>249</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B49" t="s">
-        <v>307</v>
+        <v>366</v>
       </c>
       <c r="C49" t="s">
-        <v>308</v>
+        <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="E49" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F49" t="s">
-        <v>309</v>
+        <v>491</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B50" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C50" t="s">
-        <v>490</v>
+        <v>456</v>
       </c>
       <c r="D50" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E50" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F50" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B51" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C51" t="s">
-        <v>496</v>
+        <v>267</v>
       </c>
       <c r="D51" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E51" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F51" t="s">
-        <v>249</v>
+        <v>501</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B52" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C52" t="s">
-        <v>501</v>
+        <v>349</v>
       </c>
       <c r="D52" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E52" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F52" t="s">
-        <v>249</v>
+        <v>506</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>504</v>
+        <v>124</v>
       </c>
       <c r="B53" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C53" t="s">
-        <v>247</v>
+        <v>509</v>
       </c>
       <c r="D53" t="s">
-        <v>255</v>
+        <v>510</v>
       </c>
       <c r="E53" t="s">
-        <v>394</v>
+        <v>511</v>
       </c>
       <c r="F53" t="s">
-        <v>506</v>
+        <v>303</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>508</v>
+        <v>124</v>
       </c>
       <c r="B54" t="s">
-        <v>170</v>
+        <v>513</v>
       </c>
       <c r="C54" t="s">
-        <v>324</v>
+        <v>285</v>
       </c>
       <c r="D54" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E54" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F54" t="s">
-        <v>249</v>
+        <v>515</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="B55" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="C55" t="s">
-        <v>513</v>
+        <v>267</v>
       </c>
       <c r="D55" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E55" t="s">
-        <v>415</v>
+        <v>519</v>
       </c>
       <c r="F55" t="s">
-        <v>514</v>
+        <v>249</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B56" t="s">
-        <v>283</v>
+        <v>522</v>
       </c>
       <c r="C56" t="s">
-        <v>261</v>
+        <v>523</v>
       </c>
       <c r="D56" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="E56" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="F56" t="s">
-        <v>249</v>
+        <v>525</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>245</v>
+        <v>527</v>
       </c>
       <c r="B57" t="s">
-        <v>246</v>
+        <v>528</v>
       </c>
       <c r="C57" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="D57" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E57" t="s">
-        <v>520</v>
+        <v>249</v>
       </c>
       <c r="F57" t="s">
-        <v>475</v>
-      </c>
-      <c r="G57" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="B58" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="C58" t="s">
-        <v>525</v>
+        <v>267</v>
       </c>
       <c r="D58" t="s">
-        <v>526</v>
+        <v>261</v>
       </c>
       <c r="E58" t="s">
-        <v>527</v>
+        <v>478</v>
       </c>
       <c r="F58" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B59" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C59" t="s">
-        <v>532</v>
+        <v>349</v>
       </c>
       <c r="D59" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="E59" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="F59" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="B60" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C60" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="D60" t="s">
-        <v>526</v>
+        <v>261</v>
       </c>
       <c r="E60" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="F60" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B61" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C61" t="s">
-        <v>544</v>
+        <v>247</v>
       </c>
       <c r="D61" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="E61" t="s">
-        <v>545</v>
+        <v>249</v>
       </c>
       <c r="F61" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B62" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C62" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D62" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E62" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="F62" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B63" t="s">
-        <v>440</v>
+        <v>558</v>
       </c>
       <c r="C63" t="s">
         <v>247</v>
       </c>
       <c r="D63" t="s">
-        <v>399</v>
+        <v>510</v>
       </c>
       <c r="E63" t="s">
-        <v>249</v>
+        <v>559</v>
       </c>
       <c r="F63" t="s">
-        <v>441</v>
+        <v>560</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B64" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="C64" t="s">
-        <v>558</v>
+        <v>267</v>
       </c>
       <c r="D64" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="E64" t="s">
-        <v>527</v>
+        <v>564</v>
       </c>
       <c r="F64" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="B65" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C65" t="s">
-        <v>273</v>
+        <v>569</v>
       </c>
       <c r="D65" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="E65" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="F65" t="s">
-        <v>263</v>
+        <v>571</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="B66" t="s">
-        <v>440</v>
+        <v>574</v>
       </c>
       <c r="C66" t="s">
         <v>247</v>
       </c>
       <c r="D66" t="s">
-        <v>399</v>
+        <v>510</v>
       </c>
       <c r="E66" t="s">
         <v>249</v>
       </c>
       <c r="F66" t="s">
-        <v>441</v>
+        <v>575</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="B67" t="s">
-        <v>568</v>
+        <v>494</v>
       </c>
       <c r="C67" t="s">
-        <v>247</v>
+        <v>456</v>
       </c>
       <c r="D67" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E67" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="F67" t="s">
-        <v>309</v>
+        <v>496</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="B68" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="C68" t="s">
-        <v>247</v>
+        <v>582</v>
       </c>
       <c r="D68" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E68" t="s">
-        <v>325</v>
+        <v>583</v>
       </c>
       <c r="F68" t="s">
-        <v>573</v>
+        <v>368</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="B69" t="s">
-        <v>576</v>
+        <v>371</v>
       </c>
       <c r="C69" t="s">
-        <v>577</v>
+        <v>372</v>
       </c>
       <c r="D69" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E69" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="F69" t="s">
-        <v>579</v>
+        <v>287</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="B70" t="s">
-        <v>582</v>
+        <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>583</v>
+        <v>260</v>
       </c>
       <c r="D70" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E70" t="s">
-        <v>394</v>
+        <v>589</v>
       </c>
       <c r="F70" t="s">
-        <v>584</v>
+        <v>263</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="B71" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="C71" t="s">
-        <v>588</v>
+        <v>267</v>
       </c>
       <c r="D71" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="E71" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F71" t="s">
-        <v>249</v>
+        <v>594</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="B72" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="C72" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="D72" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="E72" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="F72" t="s">
-        <v>249</v>
+        <v>600</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="B73" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
       <c r="C73" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="D73" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="E73" t="s">
-        <v>589</v>
+        <v>605</v>
       </c>
       <c r="F73" t="s">
         <v>249</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>586</v>
+        <v>153</v>
       </c>
       <c r="B74" t="s">
-        <v>587</v>
+        <v>154</v>
       </c>
       <c r="C74" t="s">
-        <v>595</v>
+        <v>155</v>
       </c>
       <c r="D74" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="E74" t="s">
-        <v>589</v>
+        <v>286</v>
       </c>
       <c r="F74" t="s">
-        <v>249</v>
+        <v>607</v>
+      </c>
+      <c r="G74" t="s">
+        <v>608</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>596</v>
+        <v>609</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="B75" t="s">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="C75" t="s">
-        <v>247</v>
+        <v>349</v>
       </c>
       <c r="D75" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E75" t="s">
-        <v>436</v>
+        <v>612</v>
       </c>
       <c r="F75" t="s">
-        <v>599</v>
+        <v>269</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>600</v>
+        <v>613</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="B76" t="s">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="C76" t="s">
         <v>247</v>
       </c>
       <c r="D76" t="s">
-        <v>255</v>
+        <v>510</v>
       </c>
       <c r="E76" t="s">
-        <v>474</v>
+        <v>616</v>
       </c>
       <c r="F76" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="B77" t="s">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="C77" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="D77" t="s">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="E77" t="s">
-        <v>394</v>
+        <v>621</v>
       </c>
       <c r="F77" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>609</v>
+        <v>624</v>
       </c>
       <c r="B78" t="s">
-        <v>288</v>
+        <v>574</v>
       </c>
       <c r="C78" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="D78" t="s">
-        <v>255</v>
+        <v>510</v>
       </c>
       <c r="E78" t="s">
-        <v>610</v>
+        <v>249</v>
       </c>
       <c r="F78" t="s">
-        <v>611</v>
+        <v>575</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>612</v>
+        <v>625</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>613</v>
+        <v>626</v>
       </c>
       <c r="B79" t="s">
-        <v>489</v>
+        <v>382</v>
       </c>
       <c r="C79" t="s">
-        <v>490</v>
+        <v>383</v>
       </c>
       <c r="D79" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E79" t="s">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="F79" t="s">
-        <v>492</v>
+        <v>384</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>615</v>
+        <v>628</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>616</v>
+        <v>629</v>
       </c>
       <c r="B80" t="s">
-        <v>388</v>
+        <v>630</v>
       </c>
       <c r="C80" t="s">
-        <v>617</v>
+        <v>631</v>
       </c>
       <c r="D80" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E80" t="s">
-        <v>618</v>
+        <v>632</v>
       </c>
       <c r="F80" t="s">
-        <v>390</v>
+        <v>633</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>619</v>
+        <v>634</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>616</v>
+        <v>635</v>
       </c>
       <c r="B81" t="s">
-        <v>388</v>
+        <v>636</v>
       </c>
       <c r="C81" t="s">
-        <v>620</v>
+        <v>637</v>
       </c>
       <c r="D81" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E81" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="F81" t="s">
-        <v>390</v>
+        <v>249</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>621</v>
+        <v>639</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>616</v>
+        <v>640</v>
       </c>
       <c r="B82" t="s">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="C82" t="s">
-        <v>622</v>
+        <v>247</v>
       </c>
       <c r="D82" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E82" t="s">
-        <v>618</v>
+        <v>570</v>
       </c>
       <c r="F82" t="s">
-        <v>390</v>
+        <v>641</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>623</v>
+        <v>642</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>624</v>
+        <v>643</v>
       </c>
       <c r="B83" t="s">
-        <v>606</v>
+        <v>337</v>
       </c>
       <c r="C83" t="s">
-        <v>254</v>
+        <v>338</v>
       </c>
       <c r="D83" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E83" t="s">
-        <v>625</v>
+        <v>644</v>
       </c>
       <c r="F83" t="s">
-        <v>626</v>
+        <v>249</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>627</v>
+        <v>645</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>628</v>
+        <v>646</v>
       </c>
       <c r="B84" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="C84" t="s">
-        <v>630</v>
+        <v>247</v>
       </c>
       <c r="D84" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E84" t="s">
-        <v>631</v>
+        <v>505</v>
       </c>
       <c r="F84" t="s">
-        <v>632</v>
+        <v>648</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>633</v>
+        <v>649</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>634</v>
+        <v>650</v>
       </c>
       <c r="B85" t="s">
-        <v>635</v>
+        <v>170</v>
       </c>
       <c r="C85" t="s">
-        <v>636</v>
+        <v>349</v>
       </c>
       <c r="D85" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E85" t="s">
-        <v>637</v>
+        <v>651</v>
       </c>
       <c r="F85" t="s">
-        <v>638</v>
+        <v>249</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>639</v>
+        <v>652</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>640</v>
+        <v>653</v>
       </c>
       <c r="B86" t="s">
-        <v>641</v>
+        <v>654</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>655</v>
       </c>
       <c r="D86" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E86" t="s">
-        <v>642</v>
+        <v>478</v>
       </c>
       <c r="F86" t="s">
-        <v>643</v>
+        <v>656</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>644</v>
+        <v>657</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>645</v>
+        <v>658</v>
       </c>
       <c r="B87" t="s">
-        <v>646</v>
+        <v>324</v>
       </c>
       <c r="C87" t="s">
-        <v>647</v>
+        <v>267</v>
       </c>
       <c r="D87" t="s">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="E87" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="F87" t="s">
-        <v>649</v>
+        <v>249</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>651</v>
+        <v>245</v>
       </c>
       <c r="B88" t="s">
-        <v>652</v>
+        <v>246</v>
       </c>
       <c r="C88" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="D88" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E88" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="F88" t="s">
-        <v>655</v>
+        <v>607</v>
+      </c>
+      <c r="G88" t="s">
+        <v>663</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>656</v>
+        <v>664</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>665</v>
+      </c>
+      <c r="B89" t="s">
+        <v>666</v>
+      </c>
+      <c r="C89" t="s">
+        <v>667</v>
+      </c>
+      <c r="D89" t="s">
+        <v>254</v>
+      </c>
+      <c r="E89" t="s">
+        <v>668</v>
+      </c>
+      <c r="F89" t="s">
+        <v>669</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>671</v>
+      </c>
+      <c r="B90" t="s">
+        <v>672</v>
+      </c>
+      <c r="C90" t="s">
+        <v>673</v>
+      </c>
+      <c r="D90" t="s">
+        <v>308</v>
+      </c>
+      <c r="E90" t="s">
+        <v>674</v>
+      </c>
+      <c r="F90" t="s">
+        <v>675</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>677</v>
+      </c>
+      <c r="B91" t="s">
+        <v>358</v>
+      </c>
+      <c r="C91" t="s">
+        <v>247</v>
+      </c>
+      <c r="D91" t="s">
+        <v>308</v>
+      </c>
+      <c r="E91" t="s">
+        <v>678</v>
+      </c>
+      <c r="F91" t="s">
+        <v>359</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>680</v>
+      </c>
+      <c r="B92" t="s">
+        <v>681</v>
+      </c>
+      <c r="C92" t="s">
+        <v>682</v>
+      </c>
+      <c r="D92" t="s">
+        <v>254</v>
+      </c>
+      <c r="E92" t="s">
+        <v>683</v>
+      </c>
+      <c r="F92" t="s">
+        <v>684</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>686</v>
+      </c>
+      <c r="B93" t="s">
+        <v>687</v>
+      </c>
+      <c r="C93" t="s">
+        <v>314</v>
+      </c>
+      <c r="D93" t="s">
+        <v>308</v>
+      </c>
+      <c r="E93" t="s">
+        <v>688</v>
+      </c>
+      <c r="F93" t="s">
+        <v>689</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>691</v>
+      </c>
+      <c r="B94" t="s">
+        <v>692</v>
+      </c>
+      <c r="C94" t="s">
+        <v>693</v>
+      </c>
+      <c r="D94" t="s">
+        <v>308</v>
+      </c>
+      <c r="E94" t="s">
+        <v>694</v>
+      </c>
+      <c r="F94" t="s">
+        <v>695</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>697</v>
+      </c>
+      <c r="B95" t="s">
+        <v>698</v>
+      </c>
+      <c r="C95" t="s">
+        <v>699</v>
+      </c>
+      <c r="D95" t="s">
+        <v>261</v>
+      </c>
+      <c r="E95" t="s">
+        <v>700</v>
+      </c>
+      <c r="F95" t="s">
+        <v>701</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>703</v>
+      </c>
+      <c r="B96" t="s">
+        <v>704</v>
+      </c>
+      <c r="C96" t="s">
+        <v>509</v>
+      </c>
+      <c r="D96" t="s">
+        <v>308</v>
+      </c>
+      <c r="E96" t="s">
+        <v>705</v>
+      </c>
+      <c r="F96" t="s">
+        <v>675</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>707</v>
+      </c>
+      <c r="B97" t="s">
+        <v>574</v>
+      </c>
+      <c r="C97" t="s">
+        <v>247</v>
+      </c>
+      <c r="D97" t="s">
+        <v>510</v>
+      </c>
+      <c r="E97" t="s">
+        <v>249</v>
+      </c>
+      <c r="F97" t="s">
+        <v>575</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>709</v>
+      </c>
+      <c r="B98" t="s">
+        <v>710</v>
+      </c>
+      <c r="C98" t="s">
+        <v>247</v>
+      </c>
+      <c r="D98" t="s">
+        <v>308</v>
+      </c>
+      <c r="E98" t="s">
+        <v>705</v>
+      </c>
+      <c r="F98" t="s">
+        <v>711</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>713</v>
+      </c>
+      <c r="B99" t="s">
+        <v>714</v>
+      </c>
+      <c r="C99" t="s">
+        <v>715</v>
+      </c>
+      <c r="D99" t="s">
+        <v>280</v>
+      </c>
+      <c r="E99" t="s">
+        <v>668</v>
+      </c>
+      <c r="F99" t="s">
+        <v>479</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>717</v>
+      </c>
+      <c r="B100" t="s">
+        <v>718</v>
+      </c>
+      <c r="C100" t="s">
+        <v>279</v>
+      </c>
+      <c r="D100" t="s">
+        <v>308</v>
+      </c>
+      <c r="E100" t="s">
+        <v>719</v>
+      </c>
+      <c r="F100" t="s">
+        <v>269</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>721</v>
+      </c>
+      <c r="B101" t="s">
+        <v>574</v>
+      </c>
+      <c r="C101" t="s">
+        <v>247</v>
+      </c>
+      <c r="D101" t="s">
+        <v>510</v>
+      </c>
+      <c r="E101" t="s">
+        <v>249</v>
+      </c>
+      <c r="F101" t="s">
+        <v>575</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>723</v>
+      </c>
+      <c r="B102" t="s">
+        <v>724</v>
+      </c>
+      <c r="C102" t="s">
+        <v>349</v>
+      </c>
+      <c r="D102" t="s">
+        <v>261</v>
+      </c>
+      <c r="E102" t="s">
+        <v>725</v>
+      </c>
+      <c r="F102" t="s">
+        <v>726</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>728</v>
+      </c>
+      <c r="B103" t="s">
+        <v>729</v>
+      </c>
+      <c r="C103" t="s">
+        <v>247</v>
+      </c>
+      <c r="D103" t="s">
+        <v>261</v>
+      </c>
+      <c r="E103" t="s">
+        <v>730</v>
+      </c>
+      <c r="F103" t="s">
+        <v>384</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>732</v>
+      </c>
+      <c r="B104" t="s">
+        <v>733</v>
+      </c>
+      <c r="C104" t="s">
+        <v>247</v>
+      </c>
+      <c r="D104" t="s">
+        <v>261</v>
+      </c>
+      <c r="E104" t="s">
+        <v>399</v>
+      </c>
+      <c r="F104" t="s">
+        <v>734</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>736</v>
+      </c>
+      <c r="B105" t="s">
+        <v>737</v>
+      </c>
+      <c r="C105" t="s">
+        <v>738</v>
+      </c>
+      <c r="D105" t="s">
+        <v>261</v>
+      </c>
+      <c r="E105" t="s">
+        <v>739</v>
+      </c>
+      <c r="F105" t="s">
+        <v>740</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>742</v>
+      </c>
+      <c r="B106" t="s">
+        <v>743</v>
+      </c>
+      <c r="C106" t="s">
+        <v>744</v>
+      </c>
+      <c r="D106" t="s">
+        <v>261</v>
+      </c>
+      <c r="E106" t="s">
+        <v>505</v>
+      </c>
+      <c r="F106" t="s">
+        <v>745</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>747</v>
+      </c>
+      <c r="B107" t="s">
+        <v>748</v>
+      </c>
+      <c r="C107" t="s">
+        <v>314</v>
+      </c>
+      <c r="D107" t="s">
+        <v>261</v>
+      </c>
+      <c r="E107" t="s">
+        <v>749</v>
+      </c>
+      <c r="F107" t="s">
+        <v>750</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>752</v>
+      </c>
+      <c r="B108" t="s">
+        <v>753</v>
+      </c>
+      <c r="C108" t="s">
+        <v>754</v>
+      </c>
+      <c r="D108" t="s">
+        <v>261</v>
+      </c>
+      <c r="E108" t="s">
+        <v>755</v>
+      </c>
+      <c r="F108" t="s">
+        <v>756</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>758</v>
+      </c>
+      <c r="B109" t="s">
+        <v>759</v>
+      </c>
+      <c r="C109" t="s">
+        <v>760</v>
+      </c>
+      <c r="D109" t="s">
+        <v>308</v>
+      </c>
+      <c r="E109" t="s">
+        <v>761</v>
+      </c>
+      <c r="F109" t="s">
+        <v>249</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>758</v>
+      </c>
+      <c r="B110" t="s">
+        <v>759</v>
+      </c>
+      <c r="C110" t="s">
+        <v>763</v>
+      </c>
+      <c r="D110" t="s">
+        <v>308</v>
+      </c>
+      <c r="E110" t="s">
+        <v>761</v>
+      </c>
+      <c r="F110" t="s">
+        <v>249</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>758</v>
+      </c>
+      <c r="B111" t="s">
+        <v>759</v>
+      </c>
+      <c r="C111" t="s">
+        <v>765</v>
+      </c>
+      <c r="D111" t="s">
+        <v>308</v>
+      </c>
+      <c r="E111" t="s">
+        <v>761</v>
+      </c>
+      <c r="F111" t="s">
+        <v>249</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>758</v>
+      </c>
+      <c r="B112" t="s">
+        <v>759</v>
+      </c>
+      <c r="C112" t="s">
+        <v>767</v>
+      </c>
+      <c r="D112" t="s">
+        <v>308</v>
+      </c>
+      <c r="E112" t="s">
+        <v>761</v>
+      </c>
+      <c r="F112" t="s">
+        <v>249</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>769</v>
+      </c>
+      <c r="B113" t="s">
+        <v>770</v>
+      </c>
+      <c r="C113" t="s">
+        <v>771</v>
+      </c>
+      <c r="D113" t="s">
+        <v>510</v>
+      </c>
+      <c r="E113" t="s">
+        <v>772</v>
+      </c>
+      <c r="F113" t="s">
+        <v>773</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>775</v>
+      </c>
+      <c r="B114" t="s">
+        <v>776</v>
+      </c>
+      <c r="C114" t="s">
+        <v>247</v>
+      </c>
+      <c r="D114" t="s">
+        <v>261</v>
+      </c>
+      <c r="E114" t="s">
+        <v>564</v>
+      </c>
+      <c r="F114" t="s">
+        <v>777</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>779</v>
+      </c>
+      <c r="B115" t="s">
+        <v>780</v>
+      </c>
+      <c r="C115" t="s">
+        <v>247</v>
+      </c>
+      <c r="D115" t="s">
+        <v>261</v>
+      </c>
+      <c r="E115" t="s">
+        <v>286</v>
+      </c>
+      <c r="F115" t="s">
+        <v>781</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>783</v>
+      </c>
+      <c r="B116" t="s">
+        <v>784</v>
+      </c>
+      <c r="C116" t="s">
+        <v>260</v>
+      </c>
+      <c r="D116" t="s">
+        <v>261</v>
+      </c>
+      <c r="E116" t="s">
+        <v>505</v>
+      </c>
+      <c r="F116" t="s">
+        <v>785</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>783</v>
+      </c>
+      <c r="B117" t="s">
+        <v>787</v>
+      </c>
+      <c r="C117" t="s">
+        <v>788</v>
+      </c>
+      <c r="D117" t="s">
+        <v>261</v>
+      </c>
+      <c r="E117" t="s">
+        <v>789</v>
+      </c>
+      <c r="F117" t="s">
+        <v>790</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>792</v>
+      </c>
+      <c r="B118" t="s">
+        <v>332</v>
+      </c>
+      <c r="C118" t="s">
+        <v>267</v>
+      </c>
+      <c r="D118" t="s">
+        <v>261</v>
+      </c>
+      <c r="E118" t="s">
+        <v>793</v>
+      </c>
+      <c r="F118" t="s">
+        <v>794</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>796</v>
+      </c>
+      <c r="B119" t="s">
+        <v>630</v>
+      </c>
+      <c r="C119" t="s">
+        <v>631</v>
+      </c>
+      <c r="D119" t="s">
+        <v>261</v>
+      </c>
+      <c r="E119" t="s">
+        <v>797</v>
+      </c>
+      <c r="F119" t="s">
+        <v>633</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>799</v>
+      </c>
+      <c r="B120" t="s">
+        <v>494</v>
+      </c>
+      <c r="C120" t="s">
+        <v>800</v>
+      </c>
+      <c r="D120" t="s">
+        <v>261</v>
+      </c>
+      <c r="E120" t="s">
+        <v>801</v>
+      </c>
+      <c r="F120" t="s">
+        <v>496</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>799</v>
+      </c>
+      <c r="B121" t="s">
+        <v>494</v>
+      </c>
+      <c r="C121" t="s">
+        <v>803</v>
+      </c>
+      <c r="D121" t="s">
+        <v>261</v>
+      </c>
+      <c r="E121" t="s">
+        <v>801</v>
+      </c>
+      <c r="F121" t="s">
+        <v>496</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>799</v>
+      </c>
+      <c r="B122" t="s">
+        <v>494</v>
+      </c>
+      <c r="C122" t="s">
+        <v>805</v>
+      </c>
+      <c r="D122" t="s">
+        <v>261</v>
+      </c>
+      <c r="E122" t="s">
+        <v>801</v>
+      </c>
+      <c r="F122" t="s">
+        <v>496</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>807</v>
+      </c>
+      <c r="B123" t="s">
+        <v>784</v>
+      </c>
+      <c r="C123" t="s">
+        <v>260</v>
+      </c>
+      <c r="D123" t="s">
+        <v>261</v>
+      </c>
+      <c r="E123" t="s">
+        <v>808</v>
+      </c>
+      <c r="F123" t="s">
+        <v>809</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>811</v>
+      </c>
+      <c r="B124" t="s">
+        <v>812</v>
+      </c>
+      <c r="C124" t="s">
+        <v>813</v>
+      </c>
+      <c r="D124" t="s">
+        <v>261</v>
+      </c>
+      <c r="E124" t="s">
+        <v>814</v>
+      </c>
+      <c r="F124" t="s">
+        <v>815</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>817</v>
+      </c>
+      <c r="B125" t="s">
+        <v>818</v>
+      </c>
+      <c r="C125" t="s">
+        <v>819</v>
+      </c>
+      <c r="D125" t="s">
+        <v>261</v>
+      </c>
+      <c r="E125" t="s">
+        <v>820</v>
+      </c>
+      <c r="F125" t="s">
+        <v>821</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>823</v>
+      </c>
+      <c r="B126" t="s">
+        <v>824</v>
+      </c>
+      <c r="C126" t="s">
+        <v>267</v>
+      </c>
+      <c r="D126" t="s">
+        <v>261</v>
+      </c>
+      <c r="E126" t="s">
+        <v>825</v>
+      </c>
+      <c r="F126" t="s">
+        <v>826</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>828</v>
+      </c>
+      <c r="B127" t="s">
+        <v>829</v>
+      </c>
+      <c r="C127" t="s">
+        <v>830</v>
+      </c>
+      <c r="D127" t="s">
+        <v>261</v>
+      </c>
+      <c r="E127" t="s">
+        <v>831</v>
+      </c>
+      <c r="F127" t="s">
+        <v>832</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>834</v>
+      </c>
+      <c r="B128" t="s">
+        <v>835</v>
+      </c>
+      <c r="C128" t="s">
+        <v>836</v>
+      </c>
+      <c r="D128" t="s">
+        <v>261</v>
+      </c>
+      <c r="E128" t="s">
+        <v>837</v>
+      </c>
+      <c r="F128" t="s">
+        <v>838</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>840</v>
+      </c>
+      <c r="B129" t="s">
+        <v>841</v>
+      </c>
+      <c r="C129" t="s">
+        <v>842</v>
+      </c>
+      <c r="D129" t="s">
+        <v>261</v>
+      </c>
+      <c r="E129" t="s">
+        <v>843</v>
+      </c>
+      <c r="F129" t="s">
+        <v>844</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>845</v>
       </c>
     </row>
   </sheetData>
@@ -5716,6 +7226,47 @@
     <hyperlink ref="H86" r:id="rId85"/>
     <hyperlink ref="H87" r:id="rId86"/>
     <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-09-14.xlsx
+++ b/docs/xlsx/jobs-2026-09-14.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="848">
   <si>
     <t>Title</t>
   </si>
@@ -2363,6 +2363,12 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/87dcb2c5d5034d9c91b664533e05bd94-sr-manager-portfolio-fund-gitlab-foundation-san-francisco</t>
+  </si>
+  <si>
+    <t>Sr. Manager, Portfolio &amp; Fund Operations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87dcb2c5d5034d9c91b664533e05bd94-sr-manager-portfolio-fund-operations-gitlab-foundation-san-francisco</t>
   </si>
   <si>
     <t>Staff Attorney</t>
@@ -4147,7 +4153,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -6819,131 +6825,131 @@
         <v>783</v>
       </c>
       <c r="B116" t="s">
+        <v>780</v>
+      </c>
+      <c r="C116" t="s">
+        <v>247</v>
+      </c>
+      <c r="D116" t="s">
+        <v>261</v>
+      </c>
+      <c r="E116" t="s">
+        <v>286</v>
+      </c>
+      <c r="F116" t="s">
+        <v>781</v>
+      </c>
+      <c r="H116" s="2" t="s">
         <v>784</v>
-      </c>
-      <c r="C116" t="s">
-        <v>260</v>
-      </c>
-      <c r="D116" t="s">
-        <v>261</v>
-      </c>
-      <c r="E116" t="s">
-        <v>505</v>
-      </c>
-      <c r="F116" t="s">
-        <v>785</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B117" t="s">
+        <v>786</v>
+      </c>
+      <c r="C117" t="s">
+        <v>260</v>
+      </c>
+      <c r="D117" t="s">
+        <v>261</v>
+      </c>
+      <c r="E117" t="s">
+        <v>505</v>
+      </c>
+      <c r="F117" t="s">
         <v>787</v>
       </c>
-      <c r="C117" t="s">
+      <c r="H117" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="D117" t="s">
-        <v>261</v>
-      </c>
-      <c r="E117" t="s">
-        <v>789</v>
-      </c>
-      <c r="F117" t="s">
-        <v>790</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>785</v>
+      </c>
+      <c r="B118" t="s">
+        <v>789</v>
+      </c>
+      <c r="C118" t="s">
+        <v>790</v>
+      </c>
+      <c r="D118" t="s">
+        <v>261</v>
+      </c>
+      <c r="E118" t="s">
+        <v>791</v>
+      </c>
+      <c r="F118" t="s">
         <v>792</v>
       </c>
-      <c r="B118" t="s">
-        <v>332</v>
-      </c>
-      <c r="C118" t="s">
-        <v>267</v>
-      </c>
-      <c r="D118" t="s">
-        <v>261</v>
-      </c>
-      <c r="E118" t="s">
+      <c r="H118" s="2" t="s">
         <v>793</v>
-      </c>
-      <c r="F118" t="s">
-        <v>794</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>794</v>
+      </c>
+      <c r="B119" t="s">
+        <v>332</v>
+      </c>
+      <c r="C119" t="s">
+        <v>267</v>
+      </c>
+      <c r="D119" t="s">
+        <v>261</v>
+      </c>
+      <c r="E119" t="s">
+        <v>795</v>
+      </c>
+      <c r="F119" t="s">
         <v>796</v>
       </c>
-      <c r="B119" t="s">
-        <v>630</v>
-      </c>
-      <c r="C119" t="s">
-        <v>631</v>
-      </c>
-      <c r="D119" t="s">
-        <v>261</v>
-      </c>
-      <c r="E119" t="s">
+      <c r="H119" s="2" t="s">
         <v>797</v>
-      </c>
-      <c r="F119" t="s">
-        <v>633</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>798</v>
+      </c>
+      <c r="B120" t="s">
+        <v>630</v>
+      </c>
+      <c r="C120" t="s">
+        <v>631</v>
+      </c>
+      <c r="D120" t="s">
+        <v>261</v>
+      </c>
+      <c r="E120" t="s">
         <v>799</v>
       </c>
-      <c r="B120" t="s">
-        <v>494</v>
-      </c>
-      <c r="C120" t="s">
+      <c r="F120" t="s">
+        <v>633</v>
+      </c>
+      <c r="H120" s="2" t="s">
         <v>800</v>
-      </c>
-      <c r="D120" t="s">
-        <v>261</v>
-      </c>
-      <c r="E120" t="s">
-        <v>801</v>
-      </c>
-      <c r="F120" t="s">
-        <v>496</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B121" t="s">
         <v>494</v>
       </c>
       <c r="C121" t="s">
+        <v>802</v>
+      </c>
+      <c r="D121" t="s">
+        <v>261</v>
+      </c>
+      <c r="E121" t="s">
         <v>803</v>
-      </c>
-      <c r="D121" t="s">
-        <v>261</v>
-      </c>
-      <c r="E121" t="s">
-        <v>801</v>
       </c>
       <c r="F121" t="s">
         <v>496</v>
@@ -6954,7 +6960,7 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B122" t="s">
         <v>494</v>
@@ -6966,7 +6972,7 @@
         <v>261</v>
       </c>
       <c r="E122" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="F122" t="s">
         <v>496</v>
@@ -6977,163 +6983,186 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>801</v>
+      </c>
+      <c r="B123" t="s">
+        <v>494</v>
+      </c>
+      <c r="C123" t="s">
         <v>807</v>
       </c>
-      <c r="B123" t="s">
-        <v>784</v>
-      </c>
-      <c r="C123" t="s">
-        <v>260</v>
-      </c>
       <c r="D123" t="s">
         <v>261</v>
       </c>
       <c r="E123" t="s">
+        <v>803</v>
+      </c>
+      <c r="F123" t="s">
+        <v>496</v>
+      </c>
+      <c r="H123" s="2" t="s">
         <v>808</v>
-      </c>
-      <c r="F123" t="s">
-        <v>809</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>809</v>
+      </c>
+      <c r="B124" t="s">
+        <v>786</v>
+      </c>
+      <c r="C124" t="s">
+        <v>260</v>
+      </c>
+      <c r="D124" t="s">
+        <v>261</v>
+      </c>
+      <c r="E124" t="s">
+        <v>810</v>
+      </c>
+      <c r="F124" t="s">
         <v>811</v>
       </c>
-      <c r="B124" t="s">
+      <c r="H124" s="2" t="s">
         <v>812</v>
-      </c>
-      <c r="C124" t="s">
-        <v>813</v>
-      </c>
-      <c r="D124" t="s">
-        <v>261</v>
-      </c>
-      <c r="E124" t="s">
-        <v>814</v>
-      </c>
-      <c r="F124" t="s">
-        <v>815</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>813</v>
+      </c>
+      <c r="B125" t="s">
+        <v>814</v>
+      </c>
+      <c r="C125" t="s">
+        <v>815</v>
+      </c>
+      <c r="D125" t="s">
+        <v>261</v>
+      </c>
+      <c r="E125" t="s">
+        <v>816</v>
+      </c>
+      <c r="F125" t="s">
         <v>817</v>
       </c>
-      <c r="B125" t="s">
+      <c r="H125" s="2" t="s">
         <v>818</v>
-      </c>
-      <c r="C125" t="s">
-        <v>819</v>
-      </c>
-      <c r="D125" t="s">
-        <v>261</v>
-      </c>
-      <c r="E125" t="s">
-        <v>820</v>
-      </c>
-      <c r="F125" t="s">
-        <v>821</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>819</v>
+      </c>
+      <c r="B126" t="s">
+        <v>820</v>
+      </c>
+      <c r="C126" t="s">
+        <v>821</v>
+      </c>
+      <c r="D126" t="s">
+        <v>261</v>
+      </c>
+      <c r="E126" t="s">
+        <v>822</v>
+      </c>
+      <c r="F126" t="s">
         <v>823</v>
       </c>
-      <c r="B126" t="s">
+      <c r="H126" s="2" t="s">
         <v>824</v>
-      </c>
-      <c r="C126" t="s">
-        <v>267</v>
-      </c>
-      <c r="D126" t="s">
-        <v>261</v>
-      </c>
-      <c r="E126" t="s">
-        <v>825</v>
-      </c>
-      <c r="F126" t="s">
-        <v>826</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>825</v>
+      </c>
+      <c r="B127" t="s">
+        <v>826</v>
+      </c>
+      <c r="C127" t="s">
+        <v>267</v>
+      </c>
+      <c r="D127" t="s">
+        <v>261</v>
+      </c>
+      <c r="E127" t="s">
+        <v>827</v>
+      </c>
+      <c r="F127" t="s">
         <v>828</v>
       </c>
-      <c r="B127" t="s">
+      <c r="H127" s="2" t="s">
         <v>829</v>
-      </c>
-      <c r="C127" t="s">
-        <v>830</v>
-      </c>
-      <c r="D127" t="s">
-        <v>261</v>
-      </c>
-      <c r="E127" t="s">
-        <v>831</v>
-      </c>
-      <c r="F127" t="s">
-        <v>832</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>830</v>
+      </c>
+      <c r="B128" t="s">
+        <v>831</v>
+      </c>
+      <c r="C128" t="s">
+        <v>832</v>
+      </c>
+      <c r="D128" t="s">
+        <v>261</v>
+      </c>
+      <c r="E128" t="s">
+        <v>833</v>
+      </c>
+      <c r="F128" t="s">
         <v>834</v>
       </c>
-      <c r="B128" t="s">
+      <c r="H128" s="2" t="s">
         <v>835</v>
-      </c>
-      <c r="C128" t="s">
-        <v>836</v>
-      </c>
-      <c r="D128" t="s">
-        <v>261</v>
-      </c>
-      <c r="E128" t="s">
-        <v>837</v>
-      </c>
-      <c r="F128" t="s">
-        <v>838</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>836</v>
+      </c>
+      <c r="B129" t="s">
+        <v>837</v>
+      </c>
+      <c r="C129" t="s">
+        <v>838</v>
+      </c>
+      <c r="D129" t="s">
+        <v>261</v>
+      </c>
+      <c r="E129" t="s">
+        <v>839</v>
+      </c>
+      <c r="F129" t="s">
         <v>840</v>
       </c>
-      <c r="B129" t="s">
+      <c r="H129" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="C129" t="s">
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
         <v>842</v>
       </c>
-      <c r="D129" t="s">
-        <v>261</v>
-      </c>
-      <c r="E129" t="s">
+      <c r="B130" t="s">
         <v>843</v>
       </c>
-      <c r="F129" t="s">
+      <c r="C130" t="s">
         <v>844</v>
       </c>
-      <c r="H129" s="2" t="s">
+      <c r="D130" t="s">
+        <v>261</v>
+      </c>
+      <c r="E130" t="s">
         <v>845</v>
+      </c>
+      <c r="F130" t="s">
+        <v>846</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>847</v>
       </c>
     </row>
   </sheetData>
@@ -7267,6 +7296,7 @@
     <hyperlink ref="H127" r:id="rId126"/>
     <hyperlink ref="H128" r:id="rId127"/>
     <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
